--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -3501,7 +3501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3525,6 +3525,11 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -3547,6 +3552,11 @@
           <t>Employee</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Lam.Le@AreteEPM.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -3569,6 +3579,11 @@
           <t>Super User</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>khuong.ngo@AreteEPM.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -3591,6 +3606,11 @@
           <t>Employee</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Wynn.Nguyen@AreteEPM.com</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -3613,6 +3633,11 @@
           <t>Employee</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wendy.Nguyen@AreteEPM.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -3635,6 +3660,11 @@
           <t>Employee</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hannah.Dinh@AreteEPM.com</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -3657,6 +3687,11 @@
           <t>Employee</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Austin.Nguyen@AreteEPM.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -3679,6 +3714,11 @@
           <t>Employee</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mia.Tran@AreteEPM.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
@@ -3701,6 +3741,11 @@
           <t>Employee</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Trung.Nguyen@AreteEPM.com</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
@@ -3721,6 +3766,11 @@
       <c r="D10" s="0" t="inlineStr">
         <is>
           <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Hanoi.Office@AreteEPM.com</t>
         </is>
       </c>
     </row>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="51.5" customWidth="1" style="3" min="2" max="2"/>
@@ -405,7 +405,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="2">
-        <f>IF(G2, TEXT(F2/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G2, TEXT(F2/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -437,39 +437,40 @@
         <v>1</v>
       </c>
       <c r="H3" s="2">
-        <f>IF(G3, TEXT(F3/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G3, TEXT(F3/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>What's New in Financial Consolidation and Close</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2">
-        <f>IF(G4, TEXT(F4/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+      <c r="C4" s="0" t="inlineStr"/>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Oracle SmartView For Financial Consolidation and Close</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>2h 40m</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="G4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0">
+        <f>IF(G4, TEXT(F4/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -486,22 +487,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>What's New in Financial Consolidation and Close</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>25m</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>158</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H5" s="2">
-        <f>IF(G5, TEXT(F5/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G5, TEXT(F5/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -518,22 +519,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="G6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <f>IF(G6, TEXT(F6/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G6, TEXT(F6/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -545,59 +546,60 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Become a Certified PCM Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM: Enterprise Profitability and Cost Management</t>
+          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14h 20m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>860</v>
+        <v>91</v>
       </c>
       <c r="G7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H7" s="2">
-        <f>IF(G7, TEXT(F7/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G7, TEXT(F7/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Become a Certified PCM Implementer</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>What's New in Enterprise Profitability and Cost Management</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47m</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="G8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2">
-        <f>IF(G8, TEXT(F8/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr"/>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>1h 30m</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="G8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0">
+        <f>IF(G8, TEXT(F8/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -614,22 +616,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Oracle Cloud EPM: Enterprise Profitability and Cost Management</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>14h 20m</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>158</v>
+        <v>860</v>
       </c>
       <c r="G9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H9" s="2">
-        <f>IF(G9, TEXT(F9/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G9, TEXT(F9/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -646,22 +648,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Oracle Profitability and Cost Management 2026 Implementation Professional (1Z0-1082-26)</t>
+          <t>What's New in Enterprise Profitability and Cost Management</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>47m</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="G10" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H10" s="2">
-        <f>IF(G10, TEXT(F10/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G10, TEXT(F10/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -673,27 +675,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Creating Reports in Cloud EPM</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2h 21m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="G11" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H11" s="2">
-        <f>IF(G11, TEXT(F11/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G11, TEXT(F11/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -705,27 +707,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Narrative Reporting Overview and Administration</t>
+          <t>Oracle Profitability and Cost Management 2026 Implementation Professional (1Z0-1082-26)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1h 39m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H12" s="2">
-        <f>IF(G12, TEXT(F12/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G12, TEXT(F12/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -742,22 +744,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Create and Manage Report Packages in Narrative Reporting</t>
+          <t>Creating Reports in Cloud EPM</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2h 0m</t>
+          <t>2h 21m</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="G13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H13" s="2">
-        <f>IF(G13, TEXT(F13/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G13, TEXT(F13/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -774,22 +776,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>What's New in Narrative Reporting</t>
+          <t>Narrative Reporting Overview and Administration</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35m</t>
+          <t>1h 39m</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="G14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H14" s="2">
-        <f>IF(G14, TEXT(F14/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G14, TEXT(F14/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -806,22 +808,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Create and Manage Report Packages in Narrative Reporting</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>2h 0m</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="G15" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H15" s="2">
-        <f>IF(G15, TEXT(F15/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G15, TEXT(F15/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -838,22 +840,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Oracle Narrative Reporting 2025 Implementation Professional (1Z0-1083-25-JPN)</t>
+          <t>What's New in Narrative Reporting</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>35m</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="G16" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H16" s="2">
-        <f>IF(G16, TEXT(F16/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G16, TEXT(F16/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -870,22 +872,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Oracle Narrative Reporting 2026 Implementation Professional (1Z0-1083-26)</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="G17" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H17" s="2">
-        <f>IF(G17, TEXT(F17/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G17, TEXT(F17/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -897,27 +899,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+          <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Integrating Data in Cloud EPM</t>
+          <t>Oracle Narrative Reporting 2025 Implementation Professional (1Z0-1083-25-JPN)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4h 43m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>283</v>
+        <v>91</v>
       </c>
       <c r="G18" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <f>IF(G18, TEXT(F18/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G18, TEXT(F18/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -929,12 +931,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+          <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
+          <t>Oracle Narrative Reporting 2026 Implementation Professional (1Z0-1083-26)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -949,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="2">
-        <f>IF(G19, TEXT(F19/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G19, TEXT(F19/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -961,27 +963,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Become a Certified Enterprise Data Management Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
+          <t>Integrating Data in Cloud EPM</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12h 25m</t>
+          <t>4h 43m</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>745</v>
+        <v>283</v>
       </c>
       <c r="G20" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H20" s="2">
-        <f>IF(G20, TEXT(F20/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G20, TEXT(F20/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -993,27 +995,27 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Become a Certified Enterprise Data Management Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>What's New in Enterprise Data Management</t>
+          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2h 1m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="2">
-        <f>IF(G21, TEXT(F21/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G21, TEXT(F21/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1030,22 +1032,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>12h 25m</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>158</v>
+        <v>745</v>
       </c>
       <c r="G22" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H22" s="2">
-        <f>IF(G22, TEXT(F22/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G22, TEXT(F22/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1062,22 +1064,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
+          <t>What's New in Enterprise Data Management</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>2h 1m</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="G23" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H23" s="2">
-        <f>IF(G23, TEXT(F23/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G23, TEXT(F23/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1094,22 +1096,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="G24" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H24" s="2">
-        <f>IF(G24, TEXT(F24/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G24, TEXT(F24/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1121,27 +1123,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM: Planning Implementation</t>
+          <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10h 17m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>617</v>
+        <v>91</v>
       </c>
       <c r="G25" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <f>IF(G25, TEXT(F25/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G25, TEXT(F25/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1153,27 +1155,27 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM: Administering Planning Modules</t>
+          <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8h 20m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H26" s="2">
-        <f>IF(G26, TEXT(F26/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G26, TEXT(F26/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1190,22 +1192,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Oracle SmartView For Planning</t>
+          <t>Oracle Cloud EPM: Planning Implementation</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>10h 17m</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>160</v>
+        <v>617</v>
       </c>
       <c r="G27" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="2">
-        <f>IF(G27, TEXT(F27/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G27, TEXT(F27/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1222,22 +1224,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>What's New in Planning</t>
+          <t>Oracle Cloud EPM: Administering Planning Modules</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41m</t>
+          <t>8h 20m</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>41</v>
+        <v>500</v>
       </c>
       <c r="G28" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H28" s="2">
-        <f>IF(G28, TEXT(F28/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G28, TEXT(F28/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1254,150 +1256,152 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Oracle SmartView For Planning</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>2h 40m</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G29" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H29" s="2">
-        <f>IF(G29, TEXT(F29/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G29, TEXT(F29/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Pigments Learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Pigment Essentials for Business Users</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Pigment Solution Overview</t>
+          <t>What's New in Planning</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>41m</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G30" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H30" s="2">
-        <f>IF(G30, TEXT(F30/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G30, TEXT(F30/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Pigments Learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Pigment Essentials for Business Users</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Pigment Applications</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>2</v>
+        <v>158</v>
       </c>
       <c r="G31" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H31" s="2">
-        <f>IF(G31, TEXT(F31/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G31, TEXT(F31/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Pigment Essentials for Business Users</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Pigment Boards</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2m</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2">
-        <f>IF(G32, TEXT(F32/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr"/>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>1h 31m</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="G32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="0">
+        <f>IF(G32, TEXT(F32/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Pigment Essentials for Business Users</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Creating Private and Public Comments</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>3m</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2">
-        <f>IF(G33, TEXT(F33/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr"/>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>1h 30m</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="G33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="0">
+        <f>IF(G33, TEXT(F33/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1414,22 +1418,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Inputting Data</t>
+          <t>Pigment Solution Overview</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G34" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H34" s="2">
-        <f>IF(G34, TEXT(F34/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G34, TEXT(F34/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1446,22 +1450,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Board Page Selectors</t>
+          <t>Pigment Applications</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="2">
-        <f>IF(G35, TEXT(F35/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G35, TEXT(F35/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1478,22 +1482,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Widget Page Selectors</t>
+          <t>Pigment Boards</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H36" s="2">
-        <f>IF(G36, TEXT(F36/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G36, TEXT(F36/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1510,22 +1514,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Changing a Widget View</t>
+          <t>Creating Private and Public Comments</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="2">
-        <f>IF(G37, TEXT(F37/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G37, TEXT(F37/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1542,22 +1546,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Downloading Data From Pigment</t>
+          <t>Inputting Data</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="2" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="2">
-        <f>IF(G38, TEXT(F38/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G38, TEXT(F38/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1569,155 +1573,155 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>Pigment Essentials for Business Users</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Board Page Selectors</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2">
+        <f>IF(G39, TEXT(F39/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Pigment Essentials for Business Users</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Widget Page Selectors</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2">
+        <f>IF(G40, TEXT(F40/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Pigment Essentials for Business Users</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Changing a Widget View</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" s="2">
+        <f>IF(G41, TEXT(F41/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Pigment Essentials for Business Users</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Downloading Data From Pigment</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2">
+        <f>IF(G42, TEXT(F42/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D39" s="0" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>Pigment Solution Overview</t>
         </is>
       </c>
-      <c r="E39" s="0" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>5m</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G39" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" s="2">
-        <f>IF(G39, TEXT(F39/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B40" s="0" t="inlineStr">
-        <is>
-          <t>Pigment Essentials for Modelers</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>Pigment and Multidimensionality</t>
-        </is>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G40" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="0">
-        <f>IF(G40, TEXT(F40/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>Pigment Essentials for Modelers</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t>Explore the Workspace</t>
-        </is>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>15m</t>
-        </is>
-      </c>
-      <c r="F41" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="G41" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" s="0">
-        <f>IF(G41, TEXT(F41/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B42" s="0" t="inlineStr">
-        <is>
-          <t>Pigment Essentials for Modelers</t>
-        </is>
-      </c>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t>Build Your First Application</t>
-        </is>
-      </c>
-      <c r="E42" s="0" t="inlineStr">
-        <is>
-          <t>20m</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="G42" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" s="0">
-        <f>IF(G42, TEXT(F42/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B43" s="0" t="inlineStr">
-        <is>
-          <t>Pigment Essentials for Modelers</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t>Work with Widgets on Boards</t>
-        </is>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="F43" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G43" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43" s="0">
-        <f>IF(G43, TEXT(F43/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+      <c r="G43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2">
+        <f>IF(G43, TEXT(F43/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1734,22 +1738,22 @@
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>Formula Structure and Syntax</t>
+          <t>Pigment and Multidimensionality</t>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>10m</t>
         </is>
       </c>
       <c r="F44" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G44" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H44" s="0">
-        <f>IF(G44, TEXT(F44/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G44, TEXT(F44/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1766,22 +1770,22 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>Use Modifiers in Formulas</t>
+          <t>Explore the Workspace</t>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>7m</t>
+          <t>15m</t>
         </is>
       </c>
       <c r="F45" s="0" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G45" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H45" s="0">
-        <f>IF(G45, TEXT(F45/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G45, TEXT(F45/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1798,22 +1802,22 @@
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>Formula Operations and Aligned Block Dimensions</t>
+          <t>Build Your First Application</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>20m</t>
         </is>
       </c>
       <c r="F46" s="0" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G46" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H46" s="0">
-        <f>IF(G46, TEXT(F46/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G46, TEXT(F46/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1830,54 +1834,54 @@
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>Please let us know what you think!</t>
+          <t>Work with Widgets on Boards</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>10m</t>
         </is>
       </c>
       <c r="F47" s="0" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G47" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H47" s="0">
-        <f>IF(G47, TEXT(F47/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G47, TEXT(F47/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>From Process to Experience: UX Design Journey</t>
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>Identify Stakeholder Needs for a Board</t>
+          <t>Formula Structure and Syntax</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>20m</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G48" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48" s="2">
-        <f>IF(G48, TEXT(F48/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" s="0">
+        <f>IF(G48, TEXT(F48/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1889,27 +1893,27 @@
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>From Process to Experience: UX Design Journey</t>
+          <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>Work with Widgets on Boards</t>
+          <t>Use Modifiers in Formulas</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>7m</t>
         </is>
       </c>
       <c r="F49" s="0" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G49" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H49" s="0">
-        <f>IF(G49, TEXT(F49/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G49, TEXT(F49/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1921,27 +1925,27 @@
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>From Process to Experience: UX Design Journey</t>
+          <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>When to Use the Different Types of Widgets on Boards</t>
+          <t>Formula Operations and Aligned Block Dimensions</t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>30m</t>
+          <t>10m</t>
         </is>
       </c>
       <c r="F50" s="0" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G50" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H50" s="0">
-        <f>IF(G50, TEXT(F50/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G50, TEXT(F50/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1953,59 +1957,59 @@
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
+          <t>Pigment Essentials for Modelers</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>Please let us know what you think!</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="0">
+        <f>IF(G51, TEXT(F51/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D51" s="0" t="inlineStr">
-        <is>
-          <t>Pigment Lists</t>
-        </is>
-      </c>
-      <c r="E51" s="0" t="inlineStr">
-        <is>
-          <t>3m</t>
-        </is>
-      </c>
-      <c r="F51" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="0">
-        <f>IF(G51, TEXT(F51/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B52" s="0" t="inlineStr">
-        <is>
-          <t>From Process to Experience: UX Design Journey</t>
-        </is>
-      </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>Pigment Lists on Boards</t>
+          <t>Identify Stakeholder Needs for a Board</t>
         </is>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>3m</t>
-        </is>
-      </c>
-      <c r="F52" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="0">
-        <f>IF(G52, TEXT(F52/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+          <t>20m</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2">
+        <f>IF(G52, TEXT(F52/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2022,22 +2026,22 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>Pigment Charts</t>
+          <t>Work with Widgets on Boards</t>
         </is>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>15m</t>
+          <t>10m</t>
         </is>
       </c>
       <c r="F53" s="0" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G53" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H53" s="0">
-        <f>IF(G53, TEXT(F53/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G53, TEXT(F53/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2054,22 +2058,22 @@
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>Page Selectors on Boards</t>
+          <t>When to Use the Different Types of Widgets on Boards</t>
         </is>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>30m</t>
         </is>
       </c>
       <c r="F54" s="0" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G54" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H54" s="0">
-        <f>IF(G54, TEXT(F54/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G54, TEXT(F54/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2086,22 +2090,22 @@
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>Adjusting Page Selectors for Business users</t>
+          <t>Pigment Lists</t>
         </is>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="F55" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G55" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H55" s="0">
-        <f>IF(G55, TEXT(F55/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G55, TEXT(F55/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2118,22 +2122,22 @@
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>Pigment Automations</t>
+          <t>Pigment Lists on Boards</t>
         </is>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="F56" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H56" s="0">
-        <f>IF(G56, TEXT(F56/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G56, TEXT(F56/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2150,59 +2154,54 @@
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>Build Boards from a Mock-up</t>
+          <t>Pigment Charts</t>
         </is>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>45m</t>
+          <t>15m</t>
         </is>
       </c>
       <c r="F57" s="0" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G57" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H57" s="0">
-        <f>IF(G57, TEXT(F57/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G57, TEXT(F57/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
-        </is>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>Read and Interpret Formulas</t>
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>Three Essential Elements for Pigment Formulas</t>
+          <t>Page Selectors on Boards</t>
         </is>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G58" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" s="2">
-        <f>IF(G58, TEXT(F58/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" s="0">
+        <f>IF(G58, TEXT(F58/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2214,32 +2213,27 @@
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
-        </is>
-      </c>
-      <c r="C59" s="0" t="inlineStr">
-        <is>
-          <t>Read and Interpret Formulas</t>
+          <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>Anatomy of a Metric</t>
+          <t>Adjusting Page Selectors for Business users</t>
         </is>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="F59" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G59" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H59" s="0">
-        <f>IF(G59, TEXT(F59/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G59, TEXT(F59/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2251,32 +2245,27 @@
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
-        </is>
-      </c>
-      <c r="C60" s="0" t="inlineStr">
-        <is>
-          <t>Read and Interpret Formulas</t>
+          <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>Introduction to Pigment Formulas</t>
+          <t>Pigment Automations</t>
         </is>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
-          <t>7m</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="F60" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G60" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H60" s="0">
-        <f>IF(G60, TEXT(F60/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G60, TEXT(F60/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2288,69 +2277,64 @@
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
+          <t>From Process to Experience: UX Design Journey</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>Build Boards from a Mock-up</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>45m</t>
+        </is>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="G61" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" s="0">
+        <f>IF(G61, TEXT(F61/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C61" s="0" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D61" s="0" t="inlineStr">
-        <is>
-          <t>Basics of Formula Writing</t>
-        </is>
-      </c>
-      <c r="E61" s="0" t="inlineStr">
-        <is>
-          <t>40m</t>
-        </is>
-      </c>
-      <c r="F61" s="0" t="n">
-        <v>40</v>
-      </c>
-      <c r="G61" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H61" s="0">
-        <f>IF(G61, TEXT(F61/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="0" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B62" s="0" t="inlineStr">
-        <is>
-          <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
-        </is>
-      </c>
-      <c r="C62" s="0" t="inlineStr">
-        <is>
-          <t>Read and Interpret Formulas</t>
-        </is>
-      </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>Introduction to Modifiers</t>
+          <t>Three Essential Elements for Pigment Formulas</t>
         </is>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
-          <t>11m</t>
-        </is>
-      </c>
-      <c r="F62" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="G62" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62" s="0">
-        <f>IF(G62, TEXT(F62/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G62" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" s="2">
+        <f>IF(G62, TEXT(F62/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2372,22 +2356,22 @@
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>Use Functions in a Formula Activity</t>
+          <t>Anatomy of a Metric</t>
         </is>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
-          <t>45m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="F63" s="0" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="G63" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H63" s="0">
-        <f>IF(G63, TEXT(F63/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G63, TEXT(F63/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2409,22 +2393,22 @@
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>Formula Playground Activity</t>
+          <t>Introduction to Pigment Formulas</t>
         </is>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t>40m</t>
+          <t>7m</t>
         </is>
       </c>
       <c r="F64" s="0" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G64" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H64" s="0">
-        <f>IF(G64, TEXT(F64/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G64, TEXT(F64/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2446,22 +2430,22 @@
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>Formula Wizard Activity</t>
+          <t>Basics of Formula Writing</t>
         </is>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
-          <t>30m</t>
+          <t>40m</t>
         </is>
       </c>
       <c r="F65" s="0" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G65" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H65" s="0">
-        <f>IF(G65, TEXT(F65/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G65, TEXT(F65/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2483,22 +2467,22 @@
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>Read and Interpret Formulas Quiz</t>
+          <t>Introduction to Modifiers</t>
         </is>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
-          <t>20m</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="F66" s="0" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G66" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H66" s="0">
-        <f>IF(G66, TEXT(F66/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G66, TEXT(F66/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2515,27 +2499,27 @@
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>Align Block Dimensions for Formulas</t>
+          <t>Read and Interpret Formulas</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>Formula Operations and Aligned Block Dimensions</t>
+          <t>Use Functions in a Formula Activity</t>
         </is>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>45m</t>
         </is>
       </c>
       <c r="F67" s="0" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G67" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H67" s="0">
-        <f>IF(G67, TEXT(F67/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G67, TEXT(F67/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2552,27 +2536,27 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>Align Block Dimensions for Formulas</t>
+          <t>Read and Interpret Formulas</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>Modifiers for Misalignment</t>
+          <t>Formula Playground Activity</t>
         </is>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>60m</t>
+          <t>40m</t>
         </is>
       </c>
       <c r="F68" s="0" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G68" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H68" s="0">
-        <f>IF(G68, TEXT(F68/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G68, TEXT(F68/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2589,27 +2573,27 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Align Block Dimensions for Formulas</t>
+          <t>Read and Interpret Formulas</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>Interactive Source to Target Mapping Tool</t>
+          <t>Formula Wizard Activity</t>
         </is>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>30m</t>
         </is>
       </c>
       <c r="F69" s="0" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G69" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H69" s="0">
-        <f>IF(G69, TEXT(F69/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G69, TEXT(F69/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2626,27 +2610,27 @@
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Align Block Dimensions for Formulas</t>
+          <t>Read and Interpret Formulas</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>Work with Dimensionality in Formulas</t>
+          <t>Read and Interpret Formulas Quiz</t>
         </is>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
-          <t>1h 50m</t>
+          <t>20m</t>
         </is>
       </c>
       <c r="F70" s="0" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="G70" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H70" s="0">
-        <f>IF(G70, TEXT(F70/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G70, TEXT(F70/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2668,22 +2652,22 @@
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>Align Block Dimensions for Formula Operations</t>
+          <t>Formula Operations and Aligned Block Dimensions</t>
         </is>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
-          <t>60m</t>
+          <t>10m</t>
         </is>
       </c>
       <c r="F71" s="0" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G71" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H71" s="0">
-        <f>IF(G71, TEXT(F71/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G71, TEXT(F71/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2705,22 +2689,22 @@
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>Please let us know what you think!</t>
+          <t>Modifiers for Misalignment</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>60m</t>
         </is>
       </c>
       <c r="F72" s="0" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="G72" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H72" s="0">
-        <f>IF(G72, TEXT(F72/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G72, TEXT(F72/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2737,27 +2721,27 @@
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Write and Test Formulas</t>
+          <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>Modifiers for Data Adjustment</t>
+          <t>Interactive Source to Target Mapping Tool</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>60m</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="F73" s="0" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G73" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H73" s="0">
-        <f>IF(G73, TEXT(F73/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G73, TEXT(F73/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2774,27 +2758,27 @@
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Write and Test Formulas</t>
+          <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>ADD, REMOVE and KEEP Modifiers</t>
+          <t>Work with Dimensionality in Formulas</t>
         </is>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
-          <t>60m</t>
+          <t>1h 50m</t>
         </is>
       </c>
       <c r="F74" s="0" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G74" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H74" s="0">
-        <f>IF(G74, TEXT(F74/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G74, TEXT(F74/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2811,27 +2795,27 @@
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Write and Test Formulas</t>
+          <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>FILTER &amp; EXCLUDE Modifiers</t>
+          <t>Align Block Dimensions for Formula Operations</t>
         </is>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
-          <t>45m</t>
+          <t>60m</t>
         </is>
       </c>
       <c r="F75" s="0" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G75" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H75" s="0">
-        <f>IF(G75, TEXT(F75/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G75, TEXT(F75/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2848,27 +2832,27 @@
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Write and Test Formulas</t>
+          <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>BY Modifier</t>
+          <t>Please let us know what you think!</t>
         </is>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="F76" s="0" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="G76" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H76" s="0">
-        <f>IF(G76, TEXT(F76/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G76, TEXT(F76/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2890,22 +2874,22 @@
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>BY -&gt; Modifier</t>
+          <t>Modifiers for Data Adjustment</t>
         </is>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>60m</t>
         </is>
       </c>
       <c r="F77" s="0" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G77" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H77" s="0">
-        <f>IF(G77, TEXT(F77/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G77, TEXT(F77/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2927,7 +2911,7 @@
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>SELECT Modifier</t>
+          <t>ADD, REMOVE and KEEP Modifiers</t>
         </is>
       </c>
       <c r="E78" s="0" t="inlineStr">
@@ -2942,7 +2926,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="0">
-        <f>IF(G78, TEXT(F78/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G78, TEXT(F78/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -2964,54 +2948,59 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>Apply Modifiers in Formulas Exercise Guide</t>
+          <t>FILTER &amp; EXCLUDE Modifiers</t>
         </is>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>3h 30m</t>
+          <t>45m</t>
         </is>
       </c>
       <c r="F79" s="0" t="n">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="G79" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H79" s="0">
-        <f>IF(G79, TEXT(F79/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G79, TEXT(F79/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Pigment Pro Training 2.0</t>
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>Pigment Pro Training - Basic Path</t>
+          <t>Write and Test Formulas</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>Attestation - Pro Training</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H80" s="2">
-        <f>IF(G80, TEXT(F80/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+          <t>BY Modifier</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="F80" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="G80" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" s="0">
+        <f>IF(G80, TEXT(F80/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3023,27 +3012,32 @@
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>Pigment Pro Training 2.0</t>
+          <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>Pigment Pro Training - Basic Path</t>
+          <t>Write and Test Formulas</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>1. Intro &amp; Understanding Business Requirements</t>
+          <t>BY -&gt; Modifier</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="F81" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G81" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H81" s="0">
-        <f>IF(G81, TEXT(F81/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G81, TEXT(F81/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3055,27 +3049,32 @@
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>Pigment Pro Training 2.0</t>
+          <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>Pigment Pro Training - Basic Path</t>
+          <t>Write and Test Formulas</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t>2. Data Hub -&gt; Step-by-Step Build</t>
+          <t>SELECT Modifier</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>60m</t>
         </is>
       </c>
       <c r="F82" s="0" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G82" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H82" s="0">
-        <f>IF(G82, TEXT(F82/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G82, TEXT(F82/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3087,59 +3086,64 @@
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
+          <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>Write and Test Formulas</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="inlineStr">
+        <is>
+          <t>Apply Modifiers in Formulas Exercise Guide</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>3h 30m</t>
+        </is>
+      </c>
+      <c r="F83" s="0" t="n">
+        <v>210</v>
+      </c>
+      <c r="G83" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" s="0">
+        <f>IF(G83, TEXT(F83/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C83" s="0" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
-      <c r="D83" s="0" t="inlineStr">
-        <is>
-          <t>3. Workforce Planning</t>
-        </is>
-      </c>
-      <c r="F83" s="0" t="n">
+      <c r="D84" s="0" t="inlineStr">
+        <is>
+          <t>Attestation - Pro Training</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G83" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83" s="0">
-        <f>IF(G83, TEXT(F83/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B84" s="0" t="inlineStr">
-        <is>
-          <t>Pigment Pro Training 2.0</t>
-        </is>
-      </c>
-      <c r="C84" s="0" t="inlineStr">
-        <is>
-          <t>Pigment Pro Training - Basic Path</t>
-        </is>
-      </c>
-      <c r="D84" s="0" t="inlineStr">
-        <is>
-          <t>Data Hub &amp; Workforce Planning Assessment</t>
-        </is>
-      </c>
-      <c r="F84" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="H84" s="0">
-        <f>IF(G84, TEXT(F84/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+      <c r="G84" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" s="2">
+        <f>IF(G84, TEXT(F84/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3156,12 +3160,12 @@
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>Pigment Pro Training - Advanced Path</t>
+          <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>4. Connecting the OpEx App</t>
+          <t>1. Intro &amp; Understanding Business Requirements</t>
         </is>
       </c>
       <c r="F85" s="0" t="n">
@@ -3171,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="0">
-        <f>IF(G85, TEXT(F85/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G85, TEXT(F85/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3188,12 +3192,12 @@
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>Pigment Pro Training - Advanced Path</t>
+          <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>Quiz: OpEX Planning</t>
+          <t>2. Data Hub -&gt; Step-by-Step Build</t>
         </is>
       </c>
       <c r="F86" s="0" t="n">
@@ -3203,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="0">
-        <f>IF(G86, TEXT(F86/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G86, TEXT(F86/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3220,12 +3224,12 @@
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>Pigment Pro Training - Advanced Path</t>
+          <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>5. Core Reporting</t>
+          <t>3. Workforce Planning</t>
         </is>
       </c>
       <c r="F87" s="0" t="n">
@@ -3235,7 +3239,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="0">
-        <f>IF(G87, TEXT(F87/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G87, TEXT(F87/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3252,12 +3256,12 @@
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>Pigment Pro Training - Advanced Path</t>
+          <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>Quiz: Core Reporting</t>
+          <t>Data Hub &amp; Workforce Planning Assessment</t>
         </is>
       </c>
       <c r="F88" s="0" t="n">
@@ -3267,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="0">
-        <f>IF(G88, TEXT(F88/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G88, TEXT(F88/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3289,7 +3293,7 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>6. Centralized Security Hub</t>
+          <t>4. Connecting the OpEx App</t>
         </is>
       </c>
       <c r="F89" s="0" t="n">
@@ -3299,7 +3303,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="0">
-        <f>IF(G89, TEXT(F89/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G89, TEXT(F89/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3321,7 +3325,7 @@
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>7. Topline Planning</t>
+          <t>Quiz: OpEX Planning</t>
         </is>
       </c>
       <c r="F90" s="0" t="n">
@@ -3331,7 +3335,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="0">
-        <f>IF(G90, TEXT(F90/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G90, TEXT(F90/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3353,7 +3357,7 @@
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>Quiz: Topline Planning</t>
+          <t>5. Core Reporting</t>
         </is>
       </c>
       <c r="F91" s="0" t="n">
@@ -3363,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="0">
-        <f>IF(G91, TEXT(F91/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G91, TEXT(F91/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3385,7 +3389,7 @@
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>8. Change Requests</t>
+          <t>Quiz: Core Reporting</t>
         </is>
       </c>
       <c r="F92" s="0" t="n">
@@ -3395,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="0">
-        <f>IF(G92, TEXT(F92/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G92, TEXT(F92/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3417,7 +3421,7 @@
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>Final Assessment</t>
+          <t>6. Centralized Security Hub</t>
         </is>
       </c>
       <c r="F93" s="0" t="n">
@@ -3427,39 +3431,39 @@
         <v>1</v>
       </c>
       <c r="H93" s="0">
-        <f>IF(G93, TEXT(F93/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G93, TEXT(F93/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Partner Application Builder Certification</t>
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>Pigment Pro Training 2.0</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>In-Person Partner App Builder Workshop</t>
-        </is>
-      </c>
-      <c r="E94" s="0" t="inlineStr">
-        <is>
-          <t>2.5 days</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G94" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H94" s="2">
-        <f>IF(G94, TEXT(F94/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+          <t>7. Topline Planning</t>
+        </is>
+      </c>
+      <c r="F94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" s="0">
+        <f>IF(G94, TEXT(F94/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3471,12 +3475,17 @@
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>Partner Application Builder Certification</t>
+          <t>Pigment Pro Training 2.0</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>Pigment Partner App Builder Certification &amp; Evaluation</t>
+          <t>Quiz: Topline Planning</t>
         </is>
       </c>
       <c r="F95" s="0" t="n">
@@ -3486,7 +3495,130 @@
         <v>1</v>
       </c>
       <c r="H95" s="0">
-        <f>IF(G95, TEXT(F95/SUMIF($G$2:$G$95, TRUE, $F$2:$F$95), "0.00%"), "0.00%")</f>
+        <f>IF(G95, TEXT(F95/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>Pigment Pro Training 2.0</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>Pigment Pro Training - Advanced Path</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t>8. Change Requests</t>
+        </is>
+      </c>
+      <c r="F96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H96" s="0">
+        <f>IF(G96, TEXT(F96/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>Pigment Pro Training 2.0</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>Pigment Pro Training - Advanced Path</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t>Final Assessment</t>
+        </is>
+      </c>
+      <c r="F97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" s="0">
+        <f>IF(G97, TEXT(F97/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Partner Application Builder Certification</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="inlineStr">
+        <is>
+          <t>In-Person Partner App Builder Workshop</t>
+        </is>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>2.5 days</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H98" s="2">
+        <f>IF(G98, TEXT(F98/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t>Partner Application Builder Certification</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="inlineStr">
+        <is>
+          <t>Pigment Partner App Builder Certification &amp; Evaluation</t>
+        </is>
+      </c>
+      <c r="F99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" s="0">
+        <f>IF(G99, TEXT(F99/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
@@ -3501,7 +3633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3525,9 +3657,19 @@
           <t>Role</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>Email</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>PasswordHash</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>MustChangePassword</t>
         </is>
       </c>
     </row>
@@ -3552,10 +3694,18 @@
           <t>Employee</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Lam.Le@AreteEPM.com</t>
         </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>130685944460738e22df8aee02a0da19$0bd762e5869440d84fb05740ee065eb2e8a11613fb6ca99774680e77106cc01f</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3579,10 +3729,18 @@
           <t>Super User</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>khuong.ngo@AreteEPM.com</t>
         </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>86df1b9ad52e7f42ffc81fac94b00df0$ce32ec48abd6cac2091d359100e9e6d41d5483e8f5f7152cb0473f8c36f9afae</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3606,10 +3764,18 @@
           <t>Employee</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Wynn.Nguyen@AreteEPM.com</t>
         </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3633,10 +3799,18 @@
           <t>Employee</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Wendy.Nguyen@AreteEPM.com</t>
         </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3660,10 +3834,18 @@
           <t>Employee</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Hannah.Dinh@AreteEPM.com</t>
         </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3687,10 +3869,18 @@
           <t>Employee</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Austin.Nguyen@AreteEPM.com</t>
         </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3714,10 +3904,18 @@
           <t>Employee</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Mia.Tran@AreteEPM.com</t>
         </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3741,10 +3939,18 @@
           <t>Employee</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Trung.Nguyen@AreteEPM.com</t>
         </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3768,10 +3974,18 @@
           <t>Manager</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Hanoi.Office@AreteEPM.com</t>
         </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>130685944460738e22df8aee02a0da19$0bd762e5869440d84fb05740ee065eb2e8a11613fb6ca99774680e77106cc01f</t>
+          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
       <c r="G2" s="0" t="b">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>86df1b9ad52e7f42ffc81fac94b00df0$ce32ec48abd6cac2091d359100e9e6d41d5483e8f5f7152cb0473f8c36f9afae</t>
+          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
       <c r="G3" s="0" t="b">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
       <c r="G4" s="0" t="b">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
       <c r="G5" s="0" t="b">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
       <c r="G6" s="0" t="b">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
       <c r="G7" s="0" t="b">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
       <c r="G8" s="0" t="b">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
       <c r="G9" s="0" t="b">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>c7888617e457914e9a1a25b6c27129e2$0694a1c2b3c8f7245586705d5aa134dcfe3eb863f505328e3dae310019eb7604</t>
+          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
       <c r="G10" s="0" t="b">

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -3736,11 +3736,11 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
+          <t>b820fffce7346444a196b3caf30f303d$a96bad452fd9deecb6a587078b6d73982e02380015642b3d70c0f4d46925a118</t>
         </is>
       </c>
       <c r="G3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -3633,7 +3633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3670,6 +3670,11 @@
       <c r="G1" s="0" t="inlineStr">
         <is>
           <t>MustChangePassword</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AvatarUrl</t>
         </is>
       </c>
     </row>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -3672,7 +3672,7 @@
           <t>MustChangePassword</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>AvatarUrl</t>
         </is>
@@ -3746,6 +3746,11 @@
       </c>
       <c r="G3" s="0" t="b">
         <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>/uploads/avatars/11_shared_image.jpg</t>
+        </is>
       </c>
     </row>
     <row r="4">

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -3747,7 +3747,7 @@
       <c r="G3" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>/uploads/avatars/11_shared_image.jpg</t>
         </is>
@@ -4075,7 +4075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4086,22 +4086,37 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>Course Name</t>
+          <t>Target Type</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
         <is>
+          <t>Target Name</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>Planned End Date</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>Workweek Type</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Daily Hours</t>
         </is>
       </c>
     </row>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -3210,21 +3210,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Creating Reports in Cloud EPM</t>
+          <t>Integrating Data in Cloud EPM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2h 21m</t>
+          <t>4h 43m</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>141</v>
+        <v>283</v>
       </c>
       <c r="G87" t="b">
         <v>1</v>
@@ -3242,21 +3242,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Narrative Reporting Overview and Administration</t>
+          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1h 39m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G88" t="b">
         <v>1</v>
@@ -3279,19 +3279,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Create and Manage Report Packages in Narrative Reporting</t>
+          <t>Creating Reports in Cloud EPM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2h 0m</t>
+          <t>2h 21m</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="G89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89">
         <f>IF(G89, TEXT(F89/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3311,19 +3311,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>What's New in Narrative Reporting</t>
+          <t>Narrative Reporting Overview and Administration</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>35m</t>
+          <t>1h 39m</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="G90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90">
         <f>IF(G90, TEXT(F90/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3343,19 +3343,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Create and Manage Report Packages in Narrative Reporting</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>2h 0m</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="G91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91">
         <f>IF(G91, TEXT(F91/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3375,19 +3375,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Oracle Narrative Reporting 2025 Implementation Professional (1Z0-1083-25-JPN)</t>
+          <t>What's New in Narrative Reporting</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>35m</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="G92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <f>IF(G92, TEXT(F92/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3407,19 +3407,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Oracle Narrative Reporting 2026 Implementation Professional (1Z0-1083-26)</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="G93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93">
         <f>IF(G93, TEXT(F93/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3434,24 +3434,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Become a Certified PCM Implementer</t>
+          <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM: Enterprise Profitability and Cost Management</t>
+          <t>Oracle Narrative Reporting 2025 Implementation Professional (1Z0-1083-25-JPN)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14h 20m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>860</v>
+        <v>91</v>
       </c>
       <c r="G94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94">
         <f>IF(G94, TEXT(F94/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3466,24 +3466,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Become a Certified PCM Implementer</t>
+          <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>What's New in Enterprise Profitability and Cost Management</t>
+          <t>Oracle Narrative Reporting 2026 Implementation Professional (1Z0-1083-26)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>47m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95">
         <f>IF(G95, TEXT(F95/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3503,19 +3503,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Oracle Cloud EPM: Enterprise Profitability and Cost Management</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>14h 20m</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>158</v>
+        <v>860</v>
       </c>
       <c r="G96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96">
         <f>IF(G96, TEXT(F96/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3535,19 +3535,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Oracle Profitability and Cost Management 2026 Implementation Professional (1Z0-1082-26)</t>
+          <t>What's New in Enterprise Profitability and Cost Management</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>47m</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="G97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97">
         <f>IF(G97, TEXT(F97/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3562,24 +3562,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+          <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Integrating Data in Cloud EPM</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>4h 43m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>283</v>
+        <v>158</v>
       </c>
       <c r="G98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98">
         <f>IF(G98, TEXT(F98/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+          <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
+          <t>Oracle Profitability and Cost Management 2026 Implementation Professional (1Z0-1082-26)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3611,7 +3611,7 @@
         <v>90</v>
       </c>
       <c r="G99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99">
         <f>IF(G99, TEXT(F99/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -2986,21 +2986,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Financial Consolidation and Close (FCC): Implementation</t>
+          <t>Integrating Data in Cloud EPM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>10h 32m</t>
+          <t>4h 43m</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>632</v>
+        <v>283</v>
       </c>
       <c r="G80" t="b">
         <v>1</v>
@@ -3018,21 +3018,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
+          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>10h 41m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>641</v>
+        <v>90</v>
       </c>
       <c r="G81" t="b">
         <v>1</v>
@@ -3055,16 +3055,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Oracle SmartView For Financial Consolidation and Close</t>
+          <t>Financial Consolidation and Close (FCC): Implementation</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>10h 32m</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>160</v>
+        <v>632</v>
       </c>
       <c r="G82" t="b">
         <v>1</v>
@@ -3087,16 +3087,16 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>What's New in Financial Consolidation and Close</t>
+          <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>25m</t>
+          <t>10h 41m</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>25</v>
+        <v>641</v>
       </c>
       <c r="G83" t="b">
         <v>1</v>
@@ -3119,19 +3119,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Oracle SmartView For Financial Consolidation and Close</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>2h 40m</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84">
         <f>IF(G84, TEXT(F84/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
@@ -3151,16 +3151,16 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
+          <t>What's New in Financial Consolidation and Close</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>25m</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="G85" t="b">
         <v>1</v>
@@ -3183,16 +3183,16 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="G86" t="b">
         <v>1</v>
@@ -3210,21 +3210,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Integrating Data in Cloud EPM</t>
+          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>4h 43m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>283</v>
+        <v>91</v>
       </c>
       <c r="G87" t="b">
         <v>1</v>
@@ -3242,12 +3242,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
+          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="51.5" customWidth="1" style="3" min="2" max="2"/>
@@ -378,3243 +378,3903 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Business Users</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>Pigment Solution Overview</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>5m</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <f>IF(G2, TEXT(F2/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="0">
+        <f>IF(G2, TEXT(F2/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Business Users</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Pigment Applications</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>2m</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <f>IF(G3, TEXT(F3/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="0">
+        <f>IF(G3, TEXT(F3/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Business Users</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>Pigment Boards</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>2m</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <f>IF(G4, TEXT(F4/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0">
+        <f>IF(G4, TEXT(F4/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Business Users</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>Creating Private and Public Comments</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <f>IF(G5, TEXT(F5/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="0">
+        <f>IF(G5, TEXT(F5/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Business Users</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>Inputting Data</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <f>IF(G6, TEXT(F6/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="0">
+        <f>IF(G6, TEXT(F6/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Business Users</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>Board Page Selectors</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <f>IF(G7, TEXT(F7/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0">
+        <f>IF(G7, TEXT(F7/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Business Users</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>Widget Page Selectors</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <f>IF(G8, TEXT(F8/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0">
+        <f>IF(G8, TEXT(F8/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Business Users</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>Changing a Widget View</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>2m</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <f>IF(G9, TEXT(F9/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="0">
+        <f>IF(G9, TEXT(F9/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Business Users</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>Downloading Data From Pigment</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>2m</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <f>IF(G10, TEXT(F10/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="0">
+        <f>IF(G10, TEXT(F10/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>Pigment Solution Overview</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>5m</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <f>IF(G11, TEXT(F11/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="0">
+        <f>IF(G11, TEXT(F11/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>Pigment and Multidimensionality</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <f>IF(G12, TEXT(F12/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="0">
+        <f>IF(G12, TEXT(F12/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>Explore the Workspace</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>15m</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <f>IF(G13, TEXT(F13/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="0">
+        <f>IF(G13, TEXT(F13/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>Build Your First Application</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>20m</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <f>IF(G14, TEXT(F14/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="0">
+        <f>IF(G14, TEXT(F14/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>Work with Widgets on Boards</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <f>IF(G15, TEXT(F15/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="0">
+        <f>IF(G15, TEXT(F15/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>Formula Structure and Syntax</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>5m</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <f>IF(G16, TEXT(F16/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="0">
+        <f>IF(G16, TEXT(F16/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>Use Modifiers in Formulas</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>7m</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <f>IF(G17, TEXT(F17/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="0">
+        <f>IF(G17, TEXT(F17/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>Formula Operations and Aligned Block Dimensions</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <f>IF(G18, TEXT(F18/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="0">
+        <f>IF(G18, TEXT(F18/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>Pigment Essentials for Modelers</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>Please let us know what you think!</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>2m</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <f>IF(G19, TEXT(F19/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="0">
+        <f>IF(G19, TEXT(F19/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>Identify Stakeholder Needs for a Board</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>20m</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <f>IF(G20, TEXT(F20/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="0">
+        <f>IF(G20, TEXT(F20/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>Work with Widgets on Boards</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <f>IF(G21, TEXT(F21/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="0">
+        <f>IF(G21, TEXT(F21/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>When to Use the Different Types of Widgets on Boards</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>30m</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <f>IF(G22, TEXT(F22/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="0">
+        <f>IF(G22, TEXT(F22/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>Pigment Lists</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <f>IF(G23, TEXT(F23/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="0">
+        <f>IF(G23, TEXT(F23/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>Pigment Lists on Boards</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <f>IF(G24, TEXT(F24/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="0">
+        <f>IF(G24, TEXT(F24/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>Pigment Charts</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>15m</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <f>IF(G25, TEXT(F25/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="0">
+        <f>IF(G25, TEXT(F25/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>Page Selectors on Boards</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <f>IF(G26, TEXT(F26/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="0">
+        <f>IF(G26, TEXT(F26/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>Adjusting Page Selectors for Business users</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>5m</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <f>IF(G27, TEXT(F27/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="0">
+        <f>IF(G27, TEXT(F27/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>Pigment Automations</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>2m</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <f>IF(G28, TEXT(F28/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="0">
+        <f>IF(G28, TEXT(F28/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>From Process to Experience: UX Design Journey</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>Build Boards from a Mock-up</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>45m</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="G29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <f>IF(G29, TEXT(F29/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="0">
+        <f>IF(G29, TEXT(F29/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>Three Essential Elements for Pigment Formulas</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>5m</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30">
-        <f>IF(G30, TEXT(F30/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="0">
+        <f>IF(G30, TEXT(F30/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>Anatomy of a Metric</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G31" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31">
-        <f>IF(G31, TEXT(F31/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="0">
+        <f>IF(G31, TEXT(F31/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>Introduction to Pigment Formulas</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>7m</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32">
-        <f>IF(G32, TEXT(F32/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="0">
+        <f>IF(G32, TEXT(F32/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>Basics of Formula Writing</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>40m</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33">
-        <f>IF(G33, TEXT(F33/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="0">
+        <f>IF(G33, TEXT(F33/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>Introduction to Modifiers</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>11m</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="G34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34">
-        <f>IF(G34, TEXT(F34/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="0">
+        <f>IF(G34, TEXT(F34/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>Use Functions in a Formula Activity</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>45m</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="G35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35">
-        <f>IF(G35, TEXT(F35/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="0">
+        <f>IF(G35, TEXT(F35/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>Formula Playground Activity</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>40m</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <f>IF(G36, TEXT(F36/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G36" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="0">
+        <f>IF(G36, TEXT(F36/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>Formula Wizard Activity</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>30m</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="G37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37">
-        <f>IF(G37, TEXT(F37/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="0">
+        <f>IF(G37, TEXT(F37/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>Read and Interpret Formulas Quiz</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>20m</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>IF(G38, TEXT(F38/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G38" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="0">
+        <f>IF(G38, TEXT(F38/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>Formula Operations and Aligned Block Dimensions</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G39" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39">
-        <f>IF(G39, TEXT(F39/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" s="0">
+        <f>IF(G39, TEXT(F39/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>Modifiers for Misalignment</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>60m</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40">
-        <f>IF(G40, TEXT(F40/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G40" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="0">
+        <f>IF(G40, TEXT(F40/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>Interactive Source to Target Mapping Tool</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <f>IF(G41, TEXT(F41/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G41" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" s="0">
+        <f>IF(G41, TEXT(F41/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>Work with Dimensionality in Formulas</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>1h 50m</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="G42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <f>IF(G42, TEXT(F42/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G42" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" s="0">
+        <f>IF(G42, TEXT(F42/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>Align Block Dimensions for Formula Operations</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>60m</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G43" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <f>IF(G43, TEXT(F43/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G43" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" s="0">
+        <f>IF(G43, TEXT(F43/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>Align Block Dimensions for Formulas</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>Please let us know what you think!</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>2m</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G44" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <f>IF(G44, TEXT(F44/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="0">
+        <f>IF(G44, TEXT(F44/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>Write and Test Formulas</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>Modifiers for Data Adjustment</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>60m</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <f>IF(G45, TEXT(F45/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G45" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="0">
+        <f>IF(G45, TEXT(F45/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>Write and Test Formulas</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>ADD, REMOVE and KEEP Modifiers</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>60m</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G46" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <f>IF(G46, TEXT(F46/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G46" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" s="0">
+        <f>IF(G46, TEXT(F46/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>Write and Test Formulas</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>FILTER &amp; EXCLUDE Modifiers</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>45m</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="G47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <f>IF(G47, TEXT(F47/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G47" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" s="0">
+        <f>IF(G47, TEXT(F47/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>Write and Test Formulas</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>BY Modifier</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="G48" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <f>IF(G48, TEXT(F48/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G48" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" s="0">
+        <f>IF(G48, TEXT(F48/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>Write and Test Formulas</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>BY -&gt; Modifier</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H49">
-        <f>IF(G49, TEXT(F49/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G49" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H49" s="0">
+        <f>IF(G49, TEXT(F49/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>Write and Test Formulas</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>SELECT Modifier</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>60m</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G50" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50">
-        <f>IF(G50, TEXT(F50/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G50" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" s="0">
+        <f>IF(G50, TEXT(F50/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>Formula Writing: Unlocking Dimensionality and Calculations</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>Write and Test Formulas</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>Apply Modifiers in Formulas Exercise Guide</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>3h 30m</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="G51" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51">
-        <f>IF(G51, TEXT(F51/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G51" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="0">
+        <f>IF(G51, TEXT(F51/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>Attestation - Pro Training</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G52" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52">
-        <f>IF(G52, TEXT(F52/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G52" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="0">
+        <f>IF(G52, TEXT(F52/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>1. Intro &amp; Understanding Business Requirements</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G53" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53">
-        <f>IF(G53, TEXT(F53/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G53" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="0">
+        <f>IF(G53, TEXT(F53/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>2. Data Hub -&gt; Step-by-Step Build</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G54" t="b">
-        <v>1</v>
-      </c>
-      <c r="H54">
-        <f>IF(G54, TEXT(F54/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G54" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H54" s="0">
+        <f>IF(G54, TEXT(F54/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>3. Workforce Planning</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G55" t="b">
-        <v>1</v>
-      </c>
-      <c r="H55">
-        <f>IF(G55, TEXT(F55/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G55" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" s="0">
+        <f>IF(G55, TEXT(F55/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Basic Path</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>Data Hub &amp; Workforce Planning Assessment</t>
         </is>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G56" t="b">
-        <v>1</v>
-      </c>
-      <c r="H56">
-        <f>IF(G56, TEXT(F56/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G56" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" s="0">
+        <f>IF(G56, TEXT(F56/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="0" t="inlineStr">
         <is>
           <t>4. Connecting the OpEx App</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H57">
-        <f>IF(G57, TEXT(F57/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G57" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" s="0">
+        <f>IF(G57, TEXT(F57/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t>Quiz: OpEX Planning</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G58" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58">
-        <f>IF(G58, TEXT(F58/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G58" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" s="0">
+        <f>IF(G58, TEXT(F58/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t>5. Core Reporting</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G59" t="b">
-        <v>1</v>
-      </c>
-      <c r="H59">
-        <f>IF(G59, TEXT(F59/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G59" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" s="0">
+        <f>IF(G59, TEXT(F59/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>Quiz: Core Reporting</t>
         </is>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G60" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60">
-        <f>IF(G60, TEXT(F60/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" s="0">
+        <f>IF(G60, TEXT(F60/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
         <is>
           <t>6. Centralized Security Hub</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G61" t="b">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <f>IF(G61, TEXT(F61/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G61" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" s="0">
+        <f>IF(G61, TEXT(F61/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
         <is>
           <t>7. Topline Planning</t>
         </is>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G62" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62">
-        <f>IF(G62, TEXT(F62/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G62" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" s="0">
+        <f>IF(G62, TEXT(F62/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="0" t="inlineStr">
         <is>
           <t>Quiz: Topline Planning</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G63" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63">
-        <f>IF(G63, TEXT(F63/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G63" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" s="0">
+        <f>IF(G63, TEXT(F63/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="0" t="inlineStr">
         <is>
           <t>8. Change Requests</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G64" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64">
-        <f>IF(G64, TEXT(F64/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G64" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="0">
+        <f>IF(G64, TEXT(F64/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training 2.0</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>Pigment Pro Training - Advanced Path</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
         <is>
           <t>Final Assessment</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G65" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65">
-        <f>IF(G65, TEXT(F65/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G65" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="0">
+        <f>IF(G65, TEXT(F65/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>Partner Application Builder Certification</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
         <is>
           <t>In-Person Partner App Builder Workshop</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="0" t="inlineStr">
         <is>
           <t>2.5 days</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="0" t="n">
         <v>1200</v>
       </c>
-      <c r="G66" t="b">
-        <v>1</v>
-      </c>
-      <c r="H66">
-        <f>IF(G66, TEXT(F66/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G66" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" s="0">
+        <f>IF(G66, TEXT(F66/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Pigments Learning</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>Partner Application Builder Certification</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
         <is>
           <t>Pigment Partner App Builder Certification &amp; Evaluation</t>
         </is>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G67" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67">
-        <f>IF(G67, TEXT(F67/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G67" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" s="0">
+        <f>IF(G67, TEXT(F67/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="0" t="inlineStr">
         <is>
           <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="0" t="inlineStr">
         <is>
           <t>12h 25m</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="0" t="n">
         <v>745</v>
       </c>
-      <c r="G68" t="b">
-        <v>1</v>
-      </c>
-      <c r="H68">
-        <f>IF(G68, TEXT(F68/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G68" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" s="0">
+        <f>IF(G68, TEXT(F68/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="0" t="inlineStr">
         <is>
           <t>What's New in Enterprise Data Management</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="0" t="inlineStr">
         <is>
           <t>2h 1m</t>
         </is>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="0" t="n">
         <v>121</v>
       </c>
-      <c r="G69" t="b">
-        <v>1</v>
-      </c>
-      <c r="H69">
-        <f>IF(G69, TEXT(F69/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G69" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" s="0">
+        <f>IF(G69, TEXT(F69/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="0" t="inlineStr">
         <is>
           <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="0" t="inlineStr">
         <is>
           <t>2h 38m</t>
         </is>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="0" t="n">
         <v>158</v>
       </c>
-      <c r="G70" t="b">
-        <v>1</v>
-      </c>
-      <c r="H70">
-        <f>IF(G70, TEXT(F70/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G70" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" s="0">
+        <f>IF(G70, TEXT(F70/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="0" t="inlineStr">
         <is>
           <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="0" t="inlineStr">
         <is>
           <t>1h 31m</t>
         </is>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="0" t="n">
         <v>91</v>
       </c>
-      <c r="G71" t="b">
-        <v>1</v>
-      </c>
-      <c r="H71">
-        <f>IF(G71, TEXT(F71/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G71" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" s="0">
+        <f>IF(G71, TEXT(F71/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="0" t="inlineStr">
         <is>
           <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="0" t="inlineStr">
         <is>
           <t>1h 30m</t>
         </is>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G72" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72">
-        <f>IF(G72, TEXT(F72/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="G72" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" s="0">
+        <f>IF(G72, TEXT(F72/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr"/>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>12h 25m</t>
+        </is>
+      </c>
+      <c r="F73" s="0" t="n">
+        <v>745</v>
+      </c>
+      <c r="G73" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" s="0">
+        <f>IF(G73, TEXT(F73/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr"/>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t>What's New in Enterprise Data Management</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>2h 1m</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="G74" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" s="0">
+        <f>IF(G74, TEXT(F74/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr"/>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t>What's New for Common Cloud EPM components</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>2h 38m</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="n">
+        <v>158</v>
+      </c>
+      <c r="G75" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" s="0">
+        <f>IF(G75, TEXT(F75/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr"/>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>1h 31m</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="G76" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" s="0">
+        <f>IF(G76, TEXT(F76/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr"/>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>1h 30m</t>
+        </is>
+      </c>
+      <c r="F77" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="G77" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" s="0">
+        <f>IF(G77, TEXT(F77/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D78" s="0" t="inlineStr">
         <is>
           <t>Oracle Cloud EPM: Planning Implementation</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E78" s="0" t="inlineStr">
         <is>
           <t>10h 17m</t>
         </is>
       </c>
-      <c r="F73" t="n">
+      <c r="F78" s="0" t="n">
         <v>617</v>
       </c>
-      <c r="G73" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73">
-        <f>IF(G73, TEXT(F73/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="G78" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" s="0">
+        <f>IF(G78, TEXT(F78/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D79" s="0" t="inlineStr">
         <is>
           <t>Oracle Cloud EPM: Administering Planning Modules</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E79" s="0" t="inlineStr">
         <is>
           <t>8h 20m</t>
         </is>
       </c>
-      <c r="F74" t="n">
+      <c r="F79" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="G74" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74">
-        <f>IF(G74, TEXT(F74/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="G79" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" s="0">
+        <f>IF(G79, TEXT(F79/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D80" s="0" t="inlineStr">
         <is>
           <t>Oracle SmartView For Planning</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E80" s="0" t="inlineStr">
         <is>
           <t>2h 40m</t>
         </is>
       </c>
-      <c r="F75" t="n">
+      <c r="F80" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="G75" t="b">
-        <v>1</v>
-      </c>
-      <c r="H75">
-        <f>IF(G75, TEXT(F75/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="G80" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" s="0">
+        <f>IF(G80, TEXT(F80/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B81" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D81" s="0" t="inlineStr">
         <is>
           <t>What's New in Planning</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E81" s="0" t="inlineStr">
         <is>
           <t>41m</t>
         </is>
       </c>
-      <c r="F76" t="n">
+      <c r="F81" s="0" t="n">
         <v>41</v>
       </c>
-      <c r="G76" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76">
-        <f>IF(G76, TEXT(F76/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="G81" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" s="0">
+        <f>IF(G81, TEXT(F81/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D82" s="0" t="inlineStr">
         <is>
           <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E82" s="0" t="inlineStr">
         <is>
           <t>2h 38m</t>
         </is>
       </c>
-      <c r="F77" t="n">
+      <c r="F82" s="0" t="n">
         <v>158</v>
       </c>
-      <c r="G77" t="b">
-        <v>1</v>
-      </c>
-      <c r="H77">
-        <f>IF(G77, TEXT(F77/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="G82" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" s="0">
+        <f>IF(G82, TEXT(F82/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B83" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D83" s="0" t="inlineStr">
         <is>
           <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E83" s="0" t="inlineStr">
         <is>
           <t>1h 31m</t>
         </is>
       </c>
-      <c r="F78" t="n">
+      <c r="F83" s="0" t="n">
         <v>91</v>
       </c>
-      <c r="G78" t="b">
-        <v>1</v>
-      </c>
-      <c r="H78">
-        <f>IF(G78, TEXT(F78/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="G83" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" s="0">
+        <f>IF(G83, TEXT(F83/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D84" s="0" t="inlineStr">
         <is>
           <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E84" s="0" t="inlineStr">
         <is>
           <t>1h 30m</t>
         </is>
       </c>
-      <c r="F79" t="n">
+      <c r="F84" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G79" t="b">
-        <v>1</v>
-      </c>
-      <c r="H79">
-        <f>IF(G79, TEXT(F79/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="G84" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" s="0">
+        <f>IF(G84, TEXT(F84/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C85" s="0" t="inlineStr"/>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Cloud EPM: Planning Implementation</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t>10h 17m</t>
+        </is>
+      </c>
+      <c r="F85" s="0" t="n">
+        <v>617</v>
+      </c>
+      <c r="G85" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" s="0">
+        <f>IF(G85, TEXT(F85/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C86" s="0" t="inlineStr"/>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Cloud EPM: Administering Planning Modules</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>8h 20m</t>
+        </is>
+      </c>
+      <c r="F86" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="G86" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" s="0">
+        <f>IF(G86, TEXT(F86/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr"/>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t>Oracle SmartView For Planning</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>2h 40m</t>
+        </is>
+      </c>
+      <c r="F87" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="G87" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H87" s="0">
+        <f>IF(G87, TEXT(F87/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="inlineStr"/>
+      <c r="D88" s="0" t="inlineStr">
+        <is>
+          <t>What's New in Planning</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>41m</t>
+        </is>
+      </c>
+      <c r="F88" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="G88" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" s="0">
+        <f>IF(G88, TEXT(F88/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C89" s="0" t="inlineStr"/>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t>What's New for Common Cloud EPM components</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>2h 38m</t>
+        </is>
+      </c>
+      <c r="F89" s="0" t="n">
+        <v>158</v>
+      </c>
+      <c r="G89" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" s="0">
+        <f>IF(G89, TEXT(F89/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C90" s="0" t="inlineStr"/>
+      <c r="D90" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t>1h 31m</t>
+        </is>
+      </c>
+      <c r="F90" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="G90" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H90" s="0">
+        <f>IF(G90, TEXT(F90/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="inlineStr"/>
+      <c r="D91" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>1h 30m</t>
+        </is>
+      </c>
+      <c r="F91" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="G91" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" s="0">
+        <f>IF(G91, TEXT(F91/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B92" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D92" s="0" t="inlineStr">
         <is>
           <t>Integrating Data in Cloud EPM</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E92" s="0" t="inlineStr">
         <is>
           <t>4h 43m</t>
         </is>
       </c>
-      <c r="F80" t="n">
+      <c r="F92" s="0" t="n">
         <v>283</v>
       </c>
-      <c r="G80" t="b">
-        <v>1</v>
-      </c>
-      <c r="H80">
-        <f>IF(G80, TEXT(F80/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="G92" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H92" s="0">
+        <f>IF(G92, TEXT(F92/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B93" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D93" s="0" t="inlineStr">
         <is>
           <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E93" s="0" t="inlineStr">
         <is>
           <t>1h 30m</t>
         </is>
       </c>
-      <c r="F81" t="n">
+      <c r="F93" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G81" t="b">
-        <v>1</v>
-      </c>
-      <c r="H81">
-        <f>IF(G81, TEXT(F81/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="G93" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" s="0">
+        <f>IF(G93, TEXT(F93/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr"/>
+      <c r="D94" s="0" t="inlineStr">
+        <is>
+          <t>Integrating Data in Cloud EPM</t>
+        </is>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>4h 43m</t>
+        </is>
+      </c>
+      <c r="F94" s="0" t="n">
+        <v>283</v>
+      </c>
+      <c r="G94" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" s="0">
+        <f>IF(G94, TEXT(F94/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr"/>
+      <c r="D95" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
+        </is>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>1h 30m</t>
+        </is>
+      </c>
+      <c r="F95" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="G95" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H95" s="0">
+        <f>IF(G95, TEXT(F95/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B96" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D96" s="0" t="inlineStr">
         <is>
           <t>Financial Consolidation and Close (FCC): Implementation</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E96" s="0" t="inlineStr">
         <is>
           <t>10h 32m</t>
         </is>
       </c>
-      <c r="F82" t="n">
+      <c r="F96" s="0" t="n">
         <v>632</v>
       </c>
-      <c r="G82" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82">
-        <f>IF(G82, TEXT(F82/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="G96" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H96" s="0">
+        <f>IF(G96, TEXT(F96/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B97" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D97" s="0" t="inlineStr">
         <is>
           <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E97" s="0" t="inlineStr">
         <is>
           <t>10h 41m</t>
         </is>
       </c>
-      <c r="F83" t="n">
+      <c r="F97" s="0" t="n">
         <v>641</v>
       </c>
-      <c r="G83" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83">
-        <f>IF(G83, TEXT(F83/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="G97" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" s="0">
+        <f>IF(G97, TEXT(F97/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B98" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D98" s="0" t="inlineStr">
         <is>
           <t>Oracle SmartView For Financial Consolidation and Close</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E98" s="0" t="inlineStr">
         <is>
           <t>2h 40m</t>
         </is>
       </c>
-      <c r="F84" t="n">
+      <c r="F98" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="G84" t="b">
+      <c r="G98" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H84">
-        <f>IF(G84, TEXT(F84/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="H98" s="0">
+        <f>IF(G98, TEXT(F98/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D99" s="0" t="inlineStr">
         <is>
           <t>What's New in Financial Consolidation and Close</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E99" s="0" t="inlineStr">
         <is>
           <t>25m</t>
         </is>
       </c>
-      <c r="F85" t="n">
+      <c r="F99" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="G85" t="b">
-        <v>1</v>
-      </c>
-      <c r="H85">
-        <f>IF(G85, TEXT(F85/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="G99" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" s="0">
+        <f>IF(G99, TEXT(F99/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B100" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D100" s="0" t="inlineStr">
         <is>
           <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E100" s="0" t="inlineStr">
         <is>
           <t>2h 38m</t>
         </is>
       </c>
-      <c r="F86" t="n">
+      <c r="F100" s="0" t="n">
         <v>158</v>
       </c>
-      <c r="G86" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86">
-        <f>IF(G86, TEXT(F86/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="G100" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" s="0">
+        <f>IF(G100, TEXT(F100/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D101" s="0" t="inlineStr">
         <is>
           <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E101" s="0" t="inlineStr">
         <is>
           <t>1h 31m</t>
         </is>
       </c>
-      <c r="F87" t="n">
+      <c r="F101" s="0" t="n">
         <v>91</v>
       </c>
-      <c r="G87" t="b">
-        <v>1</v>
-      </c>
-      <c r="H87">
-        <f>IF(G87, TEXT(F87/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="G101" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" s="0">
+        <f>IF(G101, TEXT(F101/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D102" s="0" t="inlineStr">
         <is>
           <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E102" s="0" t="inlineStr">
         <is>
           <t>1h 30m</t>
         </is>
       </c>
-      <c r="F88" t="n">
+      <c r="F102" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G88" t="b">
-        <v>1</v>
-      </c>
-      <c r="H88">
-        <f>IF(G88, TEXT(F88/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="G102" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H102" s="0">
+        <f>IF(G102, TEXT(F102/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Financial Consolidation and Close (FCC): Implementation</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>10h 32m</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>632</v>
+      </c>
+      <c r="G103" t="b">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <f>IF(G103, TEXT(F103/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>10h 41m</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>641</v>
+      </c>
+      <c r="G104" t="b">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <f>IF(G104, TEXT(F104/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>What's New in Financial Consolidation and Close</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>25</v>
+      </c>
+      <c r="G105" t="b">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <f>IF(G105, TEXT(F105/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>What's New for Common Cloud EPM components</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2h 38m</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>158</v>
+      </c>
+      <c r="G106" t="b">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <f>IF(G106, TEXT(F106/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1h 31m</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>91</v>
+      </c>
+      <c r="G107" t="b">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <f>IF(G107, TEXT(F107/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1h 30m</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>90</v>
+      </c>
+      <c r="G108" t="b">
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <f>IF(G108, TEXT(F108/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D109" s="0" t="inlineStr">
         <is>
           <t>Creating Reports in Cloud EPM</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E109" s="0" t="inlineStr">
         <is>
           <t>2h 21m</t>
         </is>
       </c>
-      <c r="F89" t="n">
+      <c r="F109" s="0" t="n">
         <v>141</v>
       </c>
-      <c r="G89" t="b">
+      <c r="G109" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H89">
-        <f>IF(G89, TEXT(F89/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="H109" s="0">
+        <f>IF(G109, TEXT(F109/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B110" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D110" s="0" t="inlineStr">
         <is>
           <t>Narrative Reporting Overview and Administration</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E110" s="0" t="inlineStr">
         <is>
           <t>1h 39m</t>
         </is>
       </c>
-      <c r="F90" t="n">
+      <c r="F110" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="G90" t="b">
+      <c r="G110" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H90">
-        <f>IF(G90, TEXT(F90/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="H110" s="0">
+        <f>IF(G110, TEXT(F110/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B111" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D111" s="0" t="inlineStr">
         <is>
           <t>Create and Manage Report Packages in Narrative Reporting</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E111" s="0" t="inlineStr">
         <is>
           <t>2h 0m</t>
         </is>
       </c>
-      <c r="F91" t="n">
+      <c r="F111" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="G91" t="b">
+      <c r="G111" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H91">
-        <f>IF(G91, TEXT(F91/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="H111" s="0">
+        <f>IF(G111, TEXT(F111/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B112" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D112" s="0" t="inlineStr">
         <is>
           <t>What's New in Narrative Reporting</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E112" s="0" t="inlineStr">
         <is>
           <t>35m</t>
         </is>
       </c>
-      <c r="F92" t="n">
+      <c r="F112" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="G92" t="b">
+      <c r="G112" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H92">
-        <f>IF(G92, TEXT(F92/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="H112" s="0">
+        <f>IF(G112, TEXT(F112/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D113" s="0" t="inlineStr">
         <is>
           <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E113" s="0" t="inlineStr">
         <is>
           <t>2h 38m</t>
         </is>
       </c>
-      <c r="F93" t="n">
+      <c r="F113" s="0" t="n">
         <v>158</v>
       </c>
-      <c r="G93" t="b">
+      <c r="G113" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H93">
-        <f>IF(G93, TEXT(F93/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="H113" s="0">
+        <f>IF(G113, TEXT(F113/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D114" s="0" t="inlineStr">
         <is>
           <t>Oracle Narrative Reporting 2025 Implementation Professional (1Z0-1083-25-JPN)</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E114" s="0" t="inlineStr">
         <is>
           <t>1h 31m</t>
         </is>
       </c>
-      <c r="F94" t="n">
+      <c r="F114" s="0" t="n">
         <v>91</v>
       </c>
-      <c r="G94" t="b">
+      <c r="G114" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H94">
-        <f>IF(G94, TEXT(F94/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="H114" s="0">
+        <f>IF(G114, TEXT(F114/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B115" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D115" s="0" t="inlineStr">
         <is>
           <t>Oracle Narrative Reporting 2026 Implementation Professional (1Z0-1083-26)</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E115" s="0" t="inlineStr">
         <is>
           <t>1h 30m</t>
         </is>
       </c>
-      <c r="F95" t="n">
+      <c r="F115" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G95" t="b">
+      <c r="G115" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H95">
-        <f>IF(G95, TEXT(F95/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="H115" s="0">
+        <f>IF(G115, TEXT(F115/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B116" s="0" t="inlineStr">
         <is>
           <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D116" s="0" t="inlineStr">
         <is>
           <t>Oracle Cloud EPM: Enterprise Profitability and Cost Management</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E116" s="0" t="inlineStr">
         <is>
           <t>14h 20m</t>
         </is>
       </c>
-      <c r="F96" t="n">
+      <c r="F116" s="0" t="n">
         <v>860</v>
       </c>
-      <c r="G96" t="b">
+      <c r="G116" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H96">
-        <f>IF(G96, TEXT(F96/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="H116" s="0">
+        <f>IF(G116, TEXT(F116/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D117" s="0" t="inlineStr">
         <is>
           <t>What's New in Enterprise Profitability and Cost Management</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E117" s="0" t="inlineStr">
         <is>
           <t>47m</t>
         </is>
       </c>
-      <c r="F97" t="n">
+      <c r="F117" s="0" t="n">
         <v>47</v>
       </c>
-      <c r="G97" t="b">
+      <c r="G117" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H97">
-        <f>IF(G97, TEXT(F97/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="H117" s="0">
+        <f>IF(G117, TEXT(F117/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D118" s="0" t="inlineStr">
         <is>
           <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E118" s="0" t="inlineStr">
         <is>
           <t>2h 38m</t>
         </is>
       </c>
-      <c r="F98" t="n">
+      <c r="F118" s="0" t="n">
         <v>158</v>
       </c>
-      <c r="G98" t="b">
+      <c r="G118" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H98">
-        <f>IF(G98, TEXT(F98/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="H118" s="0">
+        <f>IF(G118, TEXT(F118/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B119" s="0" t="inlineStr">
         <is>
           <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D119" s="0" t="inlineStr">
         <is>
           <t>Oracle Profitability and Cost Management 2026 Implementation Professional (1Z0-1082-26)</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E119" s="0" t="inlineStr">
         <is>
           <t>1h 30m</t>
         </is>
       </c>
-      <c r="F99" t="n">
+      <c r="F119" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G99" t="b">
+      <c r="G119" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="H99">
-        <f>IF(G99, TEXT(F99/SUMIF($G$2:$G$99, TRUE, $F$2:$F$99), "0.00%"), "0.00%")</f>
+      <c r="H119" s="0">
+        <f>IF(G119, TEXT(F119/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -3729,199 +3729,199 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
+      <c r="C103" s="0" t="inlineStr"/>
+      <c r="D103" s="0" t="inlineStr">
         <is>
           <t>Financial Consolidation and Close (FCC): Implementation</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="0" t="inlineStr">
         <is>
           <t>10h 32m</t>
         </is>
       </c>
-      <c r="F103" t="n">
+      <c r="F103" s="0" t="n">
         <v>632</v>
       </c>
-      <c r="G103" t="b">
-        <v>1</v>
-      </c>
-      <c r="H103">
+      <c r="G103" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H103" s="0">
         <f>IF(G103, TEXT(F103/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
+      <c r="C104" s="0" t="inlineStr"/>
+      <c r="D104" s="0" t="inlineStr">
         <is>
           <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E104" s="0" t="inlineStr">
         <is>
           <t>10h 41m</t>
         </is>
       </c>
-      <c r="F104" t="n">
+      <c r="F104" s="0" t="n">
         <v>641</v>
       </c>
-      <c r="G104" t="b">
-        <v>1</v>
-      </c>
-      <c r="H104">
+      <c r="G104" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H104" s="0">
         <f>IF(G104, TEXT(F104/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
+      <c r="C105" s="0" t="inlineStr"/>
+      <c r="D105" s="0" t="inlineStr">
         <is>
           <t>What's New in Financial Consolidation and Close</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E105" s="0" t="inlineStr">
         <is>
           <t>25m</t>
         </is>
       </c>
-      <c r="F105" t="n">
+      <c r="F105" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="G105" t="b">
-        <v>1</v>
-      </c>
-      <c r="H105">
+      <c r="G105" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H105" s="0">
         <f>IF(G105, TEXT(F105/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr">
+      <c r="C106" s="0" t="inlineStr"/>
+      <c r="D106" s="0" t="inlineStr">
         <is>
           <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" s="0" t="inlineStr">
         <is>
           <t>2h 38m</t>
         </is>
       </c>
-      <c r="F106" t="n">
+      <c r="F106" s="0" t="n">
         <v>158</v>
       </c>
-      <c r="G106" t="b">
-        <v>1</v>
-      </c>
-      <c r="H106">
+      <c r="G106" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H106" s="0">
         <f>IF(G106, TEXT(F106/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr">
+      <c r="C107" s="0" t="inlineStr"/>
+      <c r="D107" s="0" t="inlineStr">
         <is>
           <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E107" s="0" t="inlineStr">
         <is>
           <t>1h 31m</t>
         </is>
       </c>
-      <c r="F107" t="n">
+      <c r="F107" s="0" t="n">
         <v>91</v>
       </c>
-      <c r="G107" t="b">
-        <v>1</v>
-      </c>
-      <c r="H107">
+      <c r="G107" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H107" s="0">
         <f>IF(G107, TEXT(F107/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="0" t="inlineStr">
         <is>
           <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr">
+      <c r="C108" s="0" t="inlineStr"/>
+      <c r="D108" s="0" t="inlineStr">
         <is>
           <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E108" s="0" t="inlineStr">
         <is>
           <t>1h 30m</t>
         </is>
       </c>
-      <c r="F108" t="n">
+      <c r="F108" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G108" t="b">
-        <v>1</v>
-      </c>
-      <c r="H108">
+      <c r="G108" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H108" s="0">
         <f>IF(G108, TEXT(F108/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
@@ -4665,7 +4665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4717,6 +4717,1366 @@
       <c r="J1" s="0" t="inlineStr">
         <is>
           <t>Tracking Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr"/>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>46249</v>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr"/>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What's New in Enterprise Data Management</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>46249</v>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr"/>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What's New for Common Cloud EPM components</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr"/>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr"/>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr"/>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Cloud EPM: Planning Implementation</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr"/>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Cloud EPM: Administering Planning Modules</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>46256</v>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr"/>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Oracle SmartView For Planning</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>46256</v>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr"/>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What's New in Planning</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr"/>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What's New for Common Cloud EPM components</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr"/>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr"/>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>46259</v>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr"/>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Integrating Data in Cloud EPM</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr"/>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr"/>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Financial Consolidation and Close (FCC): Implementation</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr"/>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr"/>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What's New in Financial Consolidation and Close</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr"/>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What's New for Common Cloud EPM components</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr"/>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr"/>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>46249</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>What's New in Enterprise Data Management</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>46249</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>What's New for Common Cloud EPM components</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Oracle Cloud EPM: Planning Implementation</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Oracle Cloud EPM: Administering Planning Modules</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>46256</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Oracle SmartView For Planning</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>46256</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>What's New in Planning</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>What's New for Common Cloud EPM components</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>46259</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Integrating Data in Cloud EPM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Financial Consolidation and Close (FCC): Implementation</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>What's New in Financial Consolidation and Close</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>What's New for Common Cloud EPM components</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>On-track</t>
         </is>
       </c>
     </row>
@@ -4731,7 +6091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4776,6 +6136,70 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -4392,7 +4392,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>khuong.ngo@AreteEPM.com</t>
+          <t>Khuong.Ngo@AreteEPM.com</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
@@ -5401,680 +5401,680 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr"/>
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr"/>
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>What's New in Enterprise Data Management</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr"/>
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr"/>
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr"/>
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr"/>
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>Oracle Cloud EPM: Planning Implementation</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr"/>
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>Oracle Cloud EPM: Administering Planning Modules</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>46256</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr"/>
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>Oracle SmartView For Planning</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>46256</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr"/>
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>What's New in Planning</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>46258</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr"/>
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>46258</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr"/>
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>46258</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr"/>
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="4" t="n">
         <v>46259</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr"/>
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>Integrating Data in Cloud EPM</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>46260</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr"/>
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>46260</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr"/>
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>Financial Consolidation and Close (FCC): Implementation</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="4" t="n">
         <v>46262</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr"/>
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>46266</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr"/>
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>What's New in Financial Consolidation and Close</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>46266</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr"/>
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>46267</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr"/>
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>46267</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr"/>
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>46267</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -4665,7 +4665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6075,6 +6075,46 @@
         <v>46267</v>
       </c>
       <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t>On-track</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr"/>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -4746,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>46260</v>
+        <v>46256</v>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>46260</v>
+        <v>46256</v>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>6</v>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -6099,7 +6099,7 @@
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="0" t="n">

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -4746,11 +4746,11 @@
         <v>0</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>On-track</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
@@ -4780,11 +4780,11 @@
         <v>0</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>On-track</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
@@ -4814,11 +4814,11 @@
         <v>0</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>On-track</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
@@ -4848,11 +4848,11 @@
         <v>0</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t>On-track</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
@@ -4882,11 +4882,11 @@
         <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t>On-track</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>46256</v>
+        <v>46254</v>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>46256</v>
+        <v>46254</v>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>46259</v>
+        <v>46256</v>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>46242</v>
+        <v>46240</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>6</v>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -4365,8 +4365,8 @@
           <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
-      <c r="G2" s="0" t="b">
-        <v>1</v>
+      <c r="G2" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4400,7 +4400,7 @@
           <t>b820fffce7346444a196b3caf30f303d$a96bad452fd9deecb6a587078b6d73982e02380015642b3d70c0f4d46925a118</t>
         </is>
       </c>
-      <c r="G3" s="0" t="b">
+      <c r="G3" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -4440,8 +4440,8 @@
           <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
-      <c r="G4" s="0" t="b">
-        <v>1</v>
+      <c r="G4" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4475,8 +4475,8 @@
           <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
-      <c r="G5" s="0" t="b">
-        <v>1</v>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4510,8 +4510,8 @@
           <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
-      <c r="G6" s="0" t="b">
-        <v>1</v>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4545,8 +4545,8 @@
           <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
-      <c r="G7" s="0" t="b">
-        <v>1</v>
+      <c r="G7" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4580,8 +4580,8 @@
           <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
-      <c r="G8" s="0" t="b">
-        <v>1</v>
+      <c r="G8" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4615,8 +4615,8 @@
           <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
-      <c r="G9" s="0" t="b">
-        <v>1</v>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4650,8 +4650,8 @@
           <t>7239983ad4895a30fc6ff854fe757073$7b71a2f00ab59d08b52e20f66c68b0b53a301dd33314eb42625d8b722c82a76b</t>
         </is>
       </c>
-      <c r="G10" s="0" t="b">
-        <v>1</v>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4739,11 +4739,14 @@
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>46246</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>46244</v>

--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Danh sách nhân viên" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Tiến độ học tập" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Đăng ký khóa học" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Plan Metadata" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -45,7 +47,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -53,6 +55,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -328,7 +331,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:L119"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="51.5" customWidth="1" style="3" min="2" max="2"/>
@@ -376,6 +379,26 @@
           <t>% of Total</t>
         </is>
       </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Module ID</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Course Order</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>Module Order</t>
+        </is>
+      </c>
+      <c r="L1" s="0" t="inlineStr">
+        <is>
+          <t>Source Module ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -408,6 +431,17 @@
         <f>IF(G2, TEXT(F2/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>mod_40096ddaa832557e</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -440,6 +474,17 @@
         <f>IF(G3, TEXT(F3/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>mod_b89b99a809c355a5</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -472,6 +517,17 @@
         <f>IF(G4, TEXT(F4/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>mod_56b745ed876e505f</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -504,6 +560,17 @@
         <f>IF(G5, TEXT(F5/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>mod_5e69fd238c505f70</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -536,6 +603,17 @@
         <f>IF(G6, TEXT(F6/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>mod_f85138560ebd5739</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -568,6 +646,17 @@
         <f>IF(G7, TEXT(F7/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>mod_c1fcecaf0da0570e</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -600,6 +689,17 @@
         <f>IF(G8, TEXT(F8/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>mod_1cd9951ae6c45862</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
@@ -632,6 +732,17 @@
         <f>IF(G9, TEXT(F9/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>mod_42f9d5ec9dfb5d0e</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
@@ -664,6 +775,17 @@
         <f>IF(G10, TEXT(F10/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>mod_5858192f73265b60</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
@@ -696,6 +818,17 @@
         <f>IF(G11, TEXT(F11/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>mod_7b9182741ed95188</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
@@ -728,6 +861,17 @@
         <f>IF(G12, TEXT(F12/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>mod_f1469e0879565c3f</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -760,6 +904,17 @@
         <f>IF(G13, TEXT(F13/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>mod_ab006bef932d55eb</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
@@ -792,6 +947,17 @@
         <f>IF(G14, TEXT(F14/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>mod_c3c7a2c78b91506d</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
@@ -824,6 +990,17 @@
         <f>IF(G15, TEXT(F15/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>mod_f21a74f27bca53fd</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
@@ -856,6 +1033,17 @@
         <f>IF(G16, TEXT(F16/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>mod_42fb7b265b7f5733</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
@@ -888,6 +1076,17 @@
         <f>IF(G17, TEXT(F17/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>mod_33014481e5e756ab</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -920,6 +1119,17 @@
         <f>IF(G18, TEXT(F18/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>mod_63ab0c9cfff752e1</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="0" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
@@ -952,6 +1162,17 @@
         <f>IF(G19, TEXT(F19/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>mod_16995544069a5f4f</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="0" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
@@ -984,6 +1205,17 @@
         <f>IF(G20, TEXT(F20/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>mod_6e9658299f335117</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
@@ -1016,6 +1248,17 @@
         <f>IF(G21, TEXT(F21/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>mod_4c98df49c99f54db</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
@@ -1048,6 +1291,17 @@
         <f>IF(G22, TEXT(F22/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>mod_b2358b2c230056a6</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
@@ -1080,6 +1334,17 @@
         <f>IF(G23, TEXT(F23/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>mod_0898f019bae55831</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
@@ -1112,6 +1377,17 @@
         <f>IF(G24, TEXT(F24/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>mod_d9f7df1902fe5fcb</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
@@ -1144,6 +1420,17 @@
         <f>IF(G25, TEXT(F25/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>mod_e60ee96a3cd15a56</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
@@ -1176,6 +1463,17 @@
         <f>IF(G26, TEXT(F26/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>mod_e830fff931785e40</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
@@ -1208,6 +1506,17 @@
         <f>IF(G27, TEXT(F27/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>mod_6177e54123835c0e</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
@@ -1240,6 +1549,17 @@
         <f>IF(G28, TEXT(F28/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>mod_008126ac3e4d50a2</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
@@ -1272,6 +1592,17 @@
         <f>IF(G29, TEXT(F29/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>mod_b3bdc1871f495621</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" s="0" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
@@ -1309,6 +1640,17 @@
         <f>IF(G30, TEXT(F30/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>mod_4b0b417bd1d556ed</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
@@ -1346,6 +1688,17 @@
         <f>IF(G31, TEXT(F31/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>mod_854c0d1ae3c3592f</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
@@ -1383,6 +1736,17 @@
         <f>IF(G32, TEXT(F32/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>mod_42148c2d57ab581e</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
@@ -1420,6 +1784,17 @@
         <f>IF(G33, TEXT(F33/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>mod_9b645d5816ad596e</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
@@ -1457,6 +1832,17 @@
         <f>IF(G34, TEXT(F34/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t>mod_dcbf7c14e22058dd</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
@@ -1494,6 +1880,17 @@
         <f>IF(G35, TEXT(F35/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>mod_756484995dc550c5</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
@@ -1531,6 +1928,17 @@
         <f>IF(G36, TEXT(F36/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I36" s="0" t="inlineStr">
+        <is>
+          <t>mod_87c8086b177a5e66</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
@@ -1568,6 +1976,17 @@
         <f>IF(G37, TEXT(F37/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>mod_5de6371ded775bf4</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" s="0" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
@@ -1605,6 +2024,17 @@
         <f>IF(G38, TEXT(F38/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>mod_169cfa8188b95910</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" s="0" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
@@ -1642,6 +2072,17 @@
         <f>IF(G39, TEXT(F39/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>mod_6cbd36a6bfde5764</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
@@ -1679,6 +2120,17 @@
         <f>IF(G40, TEXT(F40/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t>mod_c4bd089c7a045757</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
@@ -1716,6 +2168,17 @@
         <f>IF(G41, TEXT(F41/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I41" s="0" t="inlineStr">
+        <is>
+          <t>mod_8a4054c8fc9e54c3</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
@@ -1753,6 +2216,17 @@
         <f>IF(G42, TEXT(F42/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>mod_7bd8941b812b5e3c</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
@@ -1790,6 +2264,17 @@
         <f>IF(G43, TEXT(F43/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
+          <t>mod_3a9f874115d652fa</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
@@ -1827,6 +2312,17 @@
         <f>IF(G44, TEXT(F44/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>mod_381327bd026a5fbe</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
@@ -1864,6 +2360,17 @@
         <f>IF(G45, TEXT(F45/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>mod_299fffc186ec59d5</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
@@ -1901,6 +2408,17 @@
         <f>IF(G46, TEXT(F46/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t>mod_5163b9395d685bf6</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K46" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
@@ -1938,6 +2456,17 @@
         <f>IF(G47, TEXT(F47/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t>mod_bc76ab6185fa543a</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K47" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
@@ -1975,6 +2504,17 @@
         <f>IF(G48, TEXT(F48/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t>mod_b6a7c64a58d752f0</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K48" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
@@ -2012,6 +2552,17 @@
         <f>IF(G49, TEXT(F49/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t>mod_c98aecc3912c5bd1</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
@@ -2049,6 +2600,17 @@
         <f>IF(G50, TEXT(F50/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>mod_1a8d478ee7305a2e</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K50" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
@@ -2086,6 +2648,17 @@
         <f>IF(G51, TEXT(F51/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
+          <t>mod_727650187b7655e6</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K51" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
@@ -2118,6 +2691,17 @@
         <f>IF(G52, TEXT(F52/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I52" s="0" t="inlineStr">
+        <is>
+          <t>mod_beb59da2d1855d9d</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K52" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
@@ -2150,6 +2734,17 @@
         <f>IF(G53, TEXT(F53/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
+          <t>mod_b8af8ee860ad552a</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K53" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
@@ -2182,6 +2777,17 @@
         <f>IF(G54, TEXT(F54/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I54" s="0" t="inlineStr">
+        <is>
+          <t>mod_5b886e69f20f554b</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
@@ -2214,6 +2820,17 @@
         <f>IF(G55, TEXT(F55/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I55" s="0" t="inlineStr">
+        <is>
+          <t>mod_bd15653477f855a4</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K55" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
@@ -2246,6 +2863,17 @@
         <f>IF(G56, TEXT(F56/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t>mod_5f2630cad3b85192</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
@@ -2278,6 +2906,17 @@
         <f>IF(G57, TEXT(F57/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t>mod_160367836e575c39</t>
+        </is>
+      </c>
+      <c r="J57" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K57" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
@@ -2310,6 +2949,17 @@
         <f>IF(G58, TEXT(F58/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I58" s="0" t="inlineStr">
+        <is>
+          <t>mod_1866762c8fa658d1</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K58" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
@@ -2342,6 +2992,17 @@
         <f>IF(G59, TEXT(F59/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>mod_9dc9b18e95435dcb</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K59" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
@@ -2374,6 +3035,17 @@
         <f>IF(G60, TEXT(F60/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I60" s="0" t="inlineStr">
+        <is>
+          <t>mod_06b630ea656454de</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K60" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
@@ -2406,6 +3078,17 @@
         <f>IF(G61, TEXT(F61/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I61" s="0" t="inlineStr">
+        <is>
+          <t>mod_de8f7c8db08b5f7d</t>
+        </is>
+      </c>
+      <c r="J61" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K61" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
@@ -2438,6 +3121,17 @@
         <f>IF(G62, TEXT(F62/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t>mod_f4c5c25d292554e7</t>
+        </is>
+      </c>
+      <c r="J62" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K62" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
@@ -2470,6 +3164,17 @@
         <f>IF(G63, TEXT(F63/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I63" s="0" t="inlineStr">
+        <is>
+          <t>mod_695b76464e0255dd</t>
+        </is>
+      </c>
+      <c r="J63" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K63" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
@@ -2502,6 +3207,17 @@
         <f>IF(G64, TEXT(F64/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I64" s="0" t="inlineStr">
+        <is>
+          <t>mod_6912e38cc7fd5fc3</t>
+        </is>
+      </c>
+      <c r="J64" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K64" s="0" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
@@ -2534,6 +3250,17 @@
         <f>IF(G65, TEXT(F65/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t>mod_f0f10c42d7f1516d</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K65" s="0" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
@@ -2566,6 +3293,17 @@
         <f>IF(G66, TEXT(F66/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t>mod_0b4db9dbaec95712</t>
+        </is>
+      </c>
+      <c r="J66" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K66" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
@@ -2593,6 +3331,17 @@
         <f>IF(G67, TEXT(F67/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t>mod_d5cb6977633b51cb</t>
+        </is>
+      </c>
+      <c r="J67" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K67" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
@@ -2602,21 +3351,21 @@
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Enterprise Data Management Implementer</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
+          <t>Oracle Cloud EPM: Planning Implementation</t>
         </is>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>12h 25m</t>
+          <t>10h 17m</t>
         </is>
       </c>
       <c r="F68" s="0" t="n">
-        <v>745</v>
+        <v>617</v>
       </c>
       <c r="G68" s="0" t="b">
         <v>1</v>
@@ -2625,6 +3374,17 @@
         <f>IF(G68, TEXT(F68/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>mod_2032286850235295</t>
+        </is>
+      </c>
+      <c r="J68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
@@ -2634,21 +3394,21 @@
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Enterprise Data Management Implementer</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>What's New in Enterprise Data Management</t>
+          <t>Oracle Cloud EPM: Administering Planning Modules</t>
         </is>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
-          <t>2h 1m</t>
+          <t>8h 20m</t>
         </is>
       </c>
       <c r="F69" s="0" t="n">
-        <v>121</v>
+        <v>500</v>
       </c>
       <c r="G69" s="0" t="b">
         <v>1</v>
@@ -2657,6 +3417,17 @@
         <f>IF(G69, TEXT(F69/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t>mod_889a99119f945c18</t>
+        </is>
+      </c>
+      <c r="J69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
@@ -2666,21 +3437,21 @@
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Enterprise Data Management Implementer</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Oracle SmartView For Planning</t>
         </is>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>2h 40m</t>
         </is>
       </c>
       <c r="F70" s="0" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G70" s="0" t="b">
         <v>1</v>
@@ -2689,6 +3460,17 @@
         <f>IF(G70, TEXT(F70/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I70" s="0" t="inlineStr">
+        <is>
+          <t>mod_b725190ffaca5b4d</t>
+        </is>
+      </c>
+      <c r="J70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
@@ -2698,21 +3480,21 @@
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Enterprise Data Management Implementer</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
+          <t>What's New in Planning</t>
         </is>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>41m</t>
         </is>
       </c>
       <c r="F71" s="0" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="G71" s="0" t="b">
         <v>1</v>
@@ -2721,6 +3503,17 @@
         <f>IF(G71, TEXT(F71/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I71" s="0" t="inlineStr">
+        <is>
+          <t>mod_8868a9201ae855f9</t>
+        </is>
+      </c>
+      <c r="J71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
@@ -2730,21 +3523,21 @@
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Enterprise Data Management Implementer</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F72" s="0" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="G72" s="0" t="b">
         <v>1</v>
@@ -2753,31 +3546,41 @@
         <f>IF(G72, TEXT(F72/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I72" s="0" t="inlineStr">
+        <is>
+          <t>mod_687ef6dee8735114</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Enterprise Data Management Implementer</t>
-        </is>
-      </c>
-      <c r="C73" s="0" t="inlineStr"/>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
+          <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>12h 25m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F73" s="0" t="n">
-        <v>745</v>
+        <v>91</v>
       </c>
       <c r="G73" s="0" t="b">
         <v>1</v>
@@ -2786,31 +3589,41 @@
         <f>IF(G73, TEXT(F73/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
+          <t>mod_ec122ec4f4a95aee</t>
+        </is>
+      </c>
+      <c r="J73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Enterprise Data Management Implementer</t>
-        </is>
-      </c>
-      <c r="C74" s="0" t="inlineStr"/>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>What's New in Enterprise Data Management</t>
+          <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
         </is>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
-          <t>2h 1m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F74" s="0" t="n">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="G74" s="0" t="b">
         <v>1</v>
@@ -2819,11 +3632,22 @@
         <f>IF(G74, TEXT(F74/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
+          <t>mod_e1b7adca6cc35fe6</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
@@ -2831,32 +3655,42 @@
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="C75" s="0" t="inlineStr"/>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
         </is>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>12h 25m</t>
         </is>
       </c>
       <c r="F75" s="0" t="n">
-        <v>158</v>
+        <v>745</v>
       </c>
       <c r="G75" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="0">
         <f>IF(G75, TEXT(F75/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t>mod_b9a01af4bdf15da3</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
@@ -2864,32 +3698,42 @@
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="C76" s="0" t="inlineStr"/>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
+          <t>What's New in Enterprise Data Management</t>
         </is>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>2h 1m</t>
         </is>
       </c>
       <c r="F76" s="0" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="G76" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" s="0">
         <f>IF(G76, TEXT(F76/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t>mod_a68d00fc1b1f540a</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
@@ -2897,27 +3741,37 @@
           <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
-      <c r="C77" s="0" t="inlineStr"/>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F77" s="0" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="G77" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="0">
         <f>IF(G77, TEXT(F77/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t>mod_d5b9f342db225910</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
@@ -2927,29 +3781,40 @@
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM: Planning Implementation</t>
+          <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
         </is>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t>10h 17m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F78" s="0" t="n">
-        <v>617</v>
+        <v>91</v>
       </c>
       <c r="G78" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="0">
         <f>IF(G78, TEXT(F78/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t>mod_10b84e7637c659f3</t>
+        </is>
+      </c>
+      <c r="J78" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
@@ -2959,29 +3824,40 @@
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM: Administering Planning Modules</t>
+          <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
         </is>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>8h 20m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F79" s="0" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="G79" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="0">
         <f>IF(G79, TEXT(F79/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I79" s="0" t="inlineStr">
+        <is>
+          <t>mod_c7c88159d0be5cae</t>
+        </is>
+      </c>
+      <c r="J79" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K79" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
@@ -2991,29 +3867,40 @@
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>Oracle SmartView For Planning</t>
+          <t>Integrating Data in Cloud EPM</t>
         </is>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>4h 43m</t>
         </is>
       </c>
       <c r="F80" s="0" t="n">
-        <v>160</v>
+        <v>283</v>
       </c>
       <c r="G80" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" s="0">
         <f>IF(G80, TEXT(F80/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t>mod_7eaeb7f8cf5f590e</t>
+        </is>
+      </c>
+      <c r="J80" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
@@ -3023,29 +3910,40 @@
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>What's New in Planning</t>
+          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
         </is>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t>41m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F81" s="0" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="G81" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="0">
         <f>IF(G81, TEXT(F81/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t>mod_db441ccb2f775951</t>
+        </is>
+      </c>
+      <c r="J81" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K81" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
@@ -3055,29 +3953,40 @@
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Financial Consolidation and Close (FCC): Implementation</t>
         </is>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>10h 32m</t>
         </is>
       </c>
       <c r="F82" s="0" t="n">
-        <v>158</v>
+        <v>632</v>
       </c>
       <c r="G82" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" s="0">
         <f>IF(G82, TEXT(F82/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t>mod_4c828033cf4d57ad</t>
+        </is>
+      </c>
+      <c r="J82" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
@@ -3087,29 +3996,40 @@
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
+          <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
         </is>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>10h 41m</t>
         </is>
       </c>
       <c r="F83" s="0" t="n">
-        <v>91</v>
+        <v>641</v>
       </c>
       <c r="G83" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="0">
         <f>IF(G83, TEXT(F83/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t>mod_23d7d2d256c25ec4</t>
+        </is>
+      </c>
+      <c r="J83" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
@@ -3119,260 +4039,341 @@
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
+          <t>Oracle SmartView For Financial Consolidation and Close</t>
         </is>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 40m</t>
         </is>
       </c>
       <c r="F84" s="0" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="G84" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="0">
         <f>IF(G84, TEXT(F84/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I84" s="0" t="inlineStr">
+        <is>
+          <t>mod_2889d795f0c65f2f</t>
+        </is>
+      </c>
+      <c r="J84" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
-        </is>
-      </c>
-      <c r="C85" s="0" t="inlineStr"/>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM: Planning Implementation</t>
+          <t>What's New in Financial Consolidation and Close</t>
         </is>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
-          <t>10h 17m</t>
+          <t>25m</t>
         </is>
       </c>
       <c r="F85" s="0" t="n">
-        <v>617</v>
+        <v>25</v>
       </c>
       <c r="G85" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="0">
         <f>IF(G85, TEXT(F85/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I85" s="0" t="inlineStr">
+        <is>
+          <t>mod_e3cebdd2c96e5b94</t>
+        </is>
+      </c>
+      <c r="J85" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K85" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
-        </is>
-      </c>
-      <c r="C86" s="0" t="inlineStr"/>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM: Administering Planning Modules</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
-          <t>8h 20m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F86" s="0" t="n">
-        <v>500</v>
+        <v>158</v>
       </c>
       <c r="G86" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="0">
         <f>IF(G86, TEXT(F86/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
+          <t>mod_8eaeb85e70b55594</t>
+        </is>
+      </c>
+      <c r="J86" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K86" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
-        </is>
-      </c>
-      <c r="C87" s="0" t="inlineStr"/>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>Oracle SmartView For Planning</t>
+          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
         </is>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F87" s="0" t="n">
-        <v>160</v>
+        <v>91</v>
       </c>
       <c r="G87" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="0">
         <f>IF(G87, TEXT(F87/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
+          <t>mod_fa429f6d37875a7a</t>
+        </is>
+      </c>
+      <c r="J87" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K87" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
-        </is>
-      </c>
-      <c r="C88" s="0" t="inlineStr"/>
+          <t>Become a Certified FCC Implementer</t>
+        </is>
+      </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>What's New in Planning</t>
+          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
         </is>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
-          <t>41m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F88" s="0" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="G88" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" s="0">
         <f>IF(G88, TEXT(F88/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I88" s="0" t="inlineStr">
+        <is>
+          <t>mod_f794512d053c5094</t>
+        </is>
+      </c>
+      <c r="J88" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
-        </is>
-      </c>
-      <c r="C89" s="0" t="inlineStr"/>
+          <t>Become a Certified Narrative Reporting Implementer</t>
+        </is>
+      </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Creating Reports in Cloud EPM</t>
         </is>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>2h 21m</t>
         </is>
       </c>
       <c r="F89" s="0" t="n">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="G89" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="0">
         <f>IF(G89, TEXT(F89/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I89" s="0" t="inlineStr">
+        <is>
+          <t>mod_96742f67287f5e3c</t>
+        </is>
+      </c>
+      <c r="J89" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
-        </is>
-      </c>
-      <c r="C90" s="0" t="inlineStr"/>
+          <t>Become a Certified Narrative Reporting Implementer</t>
+        </is>
+      </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
+          <t>Narrative Reporting Overview and Administration</t>
         </is>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>1h 39m</t>
         </is>
       </c>
       <c r="F90" s="0" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G90" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="0">
         <f>IF(G90, TEXT(F90/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I90" s="0" t="inlineStr">
+        <is>
+          <t>mod_3b55dc6f3d22560d</t>
+        </is>
+      </c>
+      <c r="J90" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Planning Implementer</t>
-        </is>
-      </c>
-      <c r="C91" s="0" t="inlineStr"/>
+          <t>Become a Certified Narrative Reporting Implementer</t>
+        </is>
+      </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
+          <t>Create and Manage Report Packages in Narrative Reporting</t>
         </is>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 0m</t>
         </is>
       </c>
       <c r="F91" s="0" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G91" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" s="0">
         <f>IF(G91, TEXT(F91/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I91" s="0" t="inlineStr">
+        <is>
+          <t>mod_23a2ee6a5ce25ad8</t>
+        </is>
+      </c>
+      <c r="J91" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K91" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
@@ -3382,29 +4383,40 @@
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+          <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>Integrating Data in Cloud EPM</t>
+          <t>What's New in Narrative Reporting</t>
         </is>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
-          <t>4h 43m</t>
+          <t>35m</t>
         </is>
       </c>
       <c r="F92" s="0" t="n">
-        <v>283</v>
+        <v>35</v>
       </c>
       <c r="G92" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="0">
         <f>IF(G92, TEXT(F92/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I92" s="0" t="inlineStr">
+        <is>
+          <t>mod_ae1f0002dd175c5a</t>
+        </is>
+      </c>
+      <c r="J92" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
@@ -3414,78 +4426,98 @@
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
+          <t>Become a Certified Narrative Reporting Implementer</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F93" s="0" t="n">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="G93" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="0">
         <f>IF(G93, TEXT(F93/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I93" s="0" t="inlineStr">
+        <is>
+          <t>mod_6bfaadbc14d0512a</t>
+        </is>
+      </c>
+      <c r="J93" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
-        </is>
-      </c>
-      <c r="C94" s="0" t="inlineStr"/>
+          <t>Become a Certified Narrative Reporting Implementer</t>
+        </is>
+      </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>Integrating Data in Cloud EPM</t>
+          <t>Oracle Narrative Reporting 2025 Implementation Professional (1Z0-1083-25-JPN)</t>
         </is>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
-          <t>4h 43m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F94" s="0" t="n">
-        <v>283</v>
+        <v>91</v>
       </c>
       <c r="G94" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="0">
         <f>IF(G94, TEXT(F94/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I94" s="0" t="inlineStr">
+        <is>
+          <t>mod_eb1215876293564a</t>
+        </is>
+      </c>
+      <c r="J94" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K94" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+          <t>Oracle EPM</t>
         </is>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
-        </is>
-      </c>
-      <c r="C95" s="0" t="inlineStr"/>
+          <t>Become a Certified Narrative Reporting Implementer</t>
+        </is>
+      </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
+          <t>Oracle Narrative Reporting 2026 Implementation Professional (1Z0-1083-26)</t>
         </is>
       </c>
       <c r="E95" s="0" t="inlineStr">
@@ -3497,12 +4529,23 @@
         <v>90</v>
       </c>
       <c r="G95" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="0">
         <f>IF(G95, TEXT(F95/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I95" s="0" t="inlineStr">
+        <is>
+          <t>mod_d8edacf1cf36561c</t>
+        </is>
+      </c>
+      <c r="J95" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K95" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
@@ -3512,29 +4555,40 @@
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
+          <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t>Financial Consolidation and Close (FCC): Implementation</t>
+          <t>Oracle Cloud EPM: Enterprise Profitability and Cost Management</t>
         </is>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
-          <t>10h 32m</t>
+          <t>14h 20m</t>
         </is>
       </c>
       <c r="F96" s="0" t="n">
-        <v>632</v>
+        <v>860</v>
       </c>
       <c r="G96" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="0">
         <f>IF(G96, TEXT(F96/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t>mod_c1ea2bdcdfff5b88</t>
+        </is>
+      </c>
+      <c r="J96" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K96" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
@@ -3544,29 +4598,40 @@
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
+          <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
-          <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
+          <t>What's New in Enterprise Profitability and Cost Management</t>
         </is>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
-          <t>10h 41m</t>
+          <t>47m</t>
         </is>
       </c>
       <c r="F97" s="0" t="n">
-        <v>641</v>
+        <v>47</v>
       </c>
       <c r="G97" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="0">
         <f>IF(G97, TEXT(F97/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t>mod_0f6fbfc9ae7653c0</t>
+        </is>
+      </c>
+      <c r="J97" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K97" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
@@ -3576,21 +4641,21 @@
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
+          <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t>Oracle SmartView For Financial Consolidation and Close</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F98" s="0" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G98" s="0" t="b">
         <v>0</v>
@@ -3599,6 +4664,17 @@
         <f>IF(G98, TEXT(F98/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t>mod_0f30d0a5b1ff530a</t>
+        </is>
+      </c>
+      <c r="J98" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K98" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
@@ -3608,53 +4684,64 @@
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
+          <t>Become a Certified PCM Implementer</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>What's New in Financial Consolidation and Close</t>
+          <t>Oracle Profitability and Cost Management 2026 Implementation Professional (1Z0-1082-26)</t>
         </is>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
-          <t>25m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F99" s="0" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="G99" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="0">
         <f>IF(G99, TEXT(F99/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
+          <t>mod_08ec43054e715356</t>
+        </is>
+      </c>
+      <c r="J99" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K99" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Oracle Cloud EPM: Planning Implementation</t>
         </is>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>10h 17m</t>
         </is>
       </c>
       <c r="F100" s="0" t="n">
-        <v>158</v>
+        <v>617</v>
       </c>
       <c r="G100" s="0" t="b">
         <v>1</v>
@@ -3663,30 +4750,41 @@
         <f>IF(G100, TEXT(F100/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t>mod_09ac3ee975bc5f6a</t>
+        </is>
+      </c>
+      <c r="J100" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
-          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
+          <t>Oracle Cloud EPM: Administering Planning Modules</t>
         </is>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>8h 20m</t>
         </is>
       </c>
       <c r="F101" s="0" t="n">
-        <v>91</v>
+        <v>500</v>
       </c>
       <c r="G101" s="0" t="b">
         <v>1</v>
@@ -3695,30 +4793,41 @@
         <f>IF(G101, TEXT(F101/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>mod_6dbc960605d1508a</t>
+        </is>
+      </c>
+      <c r="J101" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
+          <t>Become a Certified Planning Implementer</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
+          <t>Oracle SmartView For Planning</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 40m</t>
         </is>
       </c>
       <c r="F102" s="0" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="G102" s="0" t="b">
         <v>1</v>
@@ -3727,6 +4836,17 @@
         <f>IF(G102, TEXT(F102/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>mod_2607a6c4fd83529d</t>
+        </is>
+      </c>
+      <c r="J102" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
@@ -3736,22 +4856,21 @@
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="inlineStr"/>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t>Financial Consolidation and Close (FCC): Implementation</t>
+          <t>What's New in Planning</t>
         </is>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
-          <t>10h 32m</t>
+          <t>41m</t>
         </is>
       </c>
       <c r="F103" s="0" t="n">
-        <v>632</v>
+        <v>41</v>
       </c>
       <c r="G103" s="0" t="b">
         <v>1</v>
@@ -3760,6 +4879,17 @@
         <f>IF(G103, TEXT(F103/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t>mod_b13ff0e384fd58c7</t>
+        </is>
+      </c>
+      <c r="J103" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
@@ -3769,22 +4899,21 @@
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
-        </is>
-      </c>
-      <c r="C104" s="0" t="inlineStr"/>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
-          <t>10h 41m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F104" s="0" t="n">
-        <v>641</v>
+        <v>158</v>
       </c>
       <c r="G104" s="0" t="b">
         <v>1</v>
@@ -3793,6 +4922,17 @@
         <f>IF(G104, TEXT(F104/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t>mod_6ce8d9eef86f5fb4</t>
+        </is>
+      </c>
+      <c r="J104" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
@@ -3802,22 +4942,21 @@
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
-        </is>
-      </c>
-      <c r="C105" s="0" t="inlineStr"/>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>What's New in Financial Consolidation and Close</t>
+          <t>Oracle Planning 2025 Implementation Professional (1Z0-1080-25-JPN)</t>
         </is>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
-          <t>25m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F105" s="0" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="G105" s="0" t="b">
         <v>1</v>
@@ -3826,6 +4965,17 @@
         <f>IF(G105, TEXT(F105/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t>mod_30b53fb973b05c52</t>
+        </is>
+      </c>
+      <c r="J105" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
@@ -3835,22 +4985,21 @@
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
-        </is>
-      </c>
-      <c r="C106" s="0" t="inlineStr"/>
+          <t>Become a Certified Planning Implementer</t>
+        </is>
+      </c>
       <c r="D106" s="0" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Oracle Planning + AI 2026 Implementation Professional (1Z0-1080-26)</t>
         </is>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F106" s="0" t="n">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="G106" s="0" t="b">
         <v>1</v>
@@ -3859,6 +5008,17 @@
         <f>IF(G106, TEXT(F106/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I106" s="0" t="inlineStr">
+        <is>
+          <t>mod_a296935b855d5b67</t>
+        </is>
+      </c>
+      <c r="J106" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
@@ -3868,30 +5028,40 @@
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
-        </is>
-      </c>
-      <c r="C107" s="0" t="inlineStr"/>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
       <c r="D107" s="0" t="inlineStr">
         <is>
-          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
+          <t>Manage &amp; Govern Enterprise Data Assets with Enterprise Data Management Cloud</t>
         </is>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>12h 25m</t>
         </is>
       </c>
       <c r="F107" s="0" t="n">
-        <v>91</v>
+        <v>745</v>
       </c>
       <c r="G107" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" s="0">
         <f>IF(G107, TEXT(F107/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t>mod_227a4ac970765faf</t>
+        </is>
+      </c>
+      <c r="J107" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
@@ -3901,54 +5071,64 @@
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified FCC Implementer</t>
-        </is>
-      </c>
-      <c r="C108" s="0" t="inlineStr"/>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
+        </is>
+      </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
+          <t>What's New in Enterprise Data Management</t>
         </is>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>2h 1m</t>
         </is>
       </c>
       <c r="F108" s="0" t="n">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="G108" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" s="0">
         <f>IF(G108, TEXT(F108/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t>mod_462dc0b7059255f6</t>
+        </is>
+      </c>
+      <c r="J108" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
         <is>
-          <t>Creating Reports in Cloud EPM</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
-          <t>2h 21m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F109" s="0" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="G109" s="0" t="b">
         <v>0</v>
@@ -3957,30 +5137,41 @@
         <f>IF(G109, TEXT(F109/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t>mod_d43fe969b8f7585f</t>
+        </is>
+      </c>
+      <c r="J109" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K109" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
         <is>
-          <t>Narrative Reporting Overview and Administration</t>
+          <t>Oracle Enterprise Data Management Cloud 2025 Implementation Professional (1Z0-1086-25-JPN)</t>
         </is>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
-          <t>1h 39m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F110" s="0" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G110" s="0" t="b">
         <v>0</v>
@@ -3989,30 +5180,41 @@
         <f>IF(G110, TEXT(F110/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
+          <t>mod_de85a4a7c60958b8</t>
+        </is>
+      </c>
+      <c r="J110" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K110" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified Enterprise Data Management Implementer</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
         <is>
-          <t>Create and Manage Report Packages in Narrative Reporting</t>
+          <t>Oracle Enterprise Data Management Cloud 2026 Implementation Professional (1Z0-1086-26)</t>
         </is>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
-          <t>2h 0m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F111" s="0" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G111" s="0" t="b">
         <v>0</v>
@@ -4021,30 +5223,41 @@
         <f>IF(G111, TEXT(F111/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t>mod_126d66d0c0775a75</t>
+        </is>
+      </c>
+      <c r="J111" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K111" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
         <is>
-          <t>What's New in Narrative Reporting</t>
+          <t>Integrating Data in Cloud EPM</t>
         </is>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
-          <t>35m</t>
+          <t>4h 43m</t>
         </is>
       </c>
       <c r="F112" s="0" t="n">
-        <v>35</v>
+        <v>283</v>
       </c>
       <c r="G112" s="0" t="b">
         <v>0</v>
@@ -4053,30 +5266,41 @@
         <f>IF(G112, TEXT(F112/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>mod_cca5089845875b1a</t>
+        </is>
+      </c>
+      <c r="J112" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K112" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified Oracle Cloud EPM Data Integration Implementer</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Oracle Cloud EPM Data Integration 2026 Implementation Professional (1Z0-1133-26)</t>
         </is>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>1h 30m</t>
         </is>
       </c>
       <c r="F113" s="0" t="n">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="G113" s="0" t="b">
         <v>0</v>
@@ -4085,30 +5309,41 @@
         <f>IF(G113, TEXT(F113/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t>mod_29d398f2f2cf554b</t>
+        </is>
+      </c>
+      <c r="J113" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K113" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
         <is>
-          <t>Oracle Narrative Reporting 2025 Implementation Professional (1Z0-1083-25-JPN)</t>
+          <t>Financial Consolidation and Close (FCC): Implementation</t>
         </is>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>10h 32m</t>
         </is>
       </c>
       <c r="F114" s="0" t="n">
-        <v>91</v>
+        <v>632</v>
       </c>
       <c r="G114" s="0" t="b">
         <v>0</v>
@@ -4117,30 +5352,41 @@
         <f>IF(G114, TEXT(F114/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t>mod_9f158a8eb28f5300</t>
+        </is>
+      </c>
+      <c r="J114" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K114" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified Narrative Reporting Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
         <is>
-          <t>Oracle Narrative Reporting 2026 Implementation Professional (1Z0-1083-26)</t>
+          <t>Financial Consolidation and Close (FCC): Designing the Close Process</t>
         </is>
       </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
-          <t>1h 30m</t>
+          <t>10h 41m</t>
         </is>
       </c>
       <c r="F115" s="0" t="n">
-        <v>90</v>
+        <v>641</v>
       </c>
       <c r="G115" s="0" t="b">
         <v>0</v>
@@ -4149,30 +5395,41 @@
         <f>IF(G115, TEXT(F115/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I115" s="0" t="inlineStr">
+        <is>
+          <t>mod_3122658003f05166</t>
+        </is>
+      </c>
+      <c r="J115" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K115" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified PCM Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
         <is>
-          <t>Oracle Cloud EPM: Enterprise Profitability and Cost Management</t>
+          <t>What's New in Financial Consolidation and Close</t>
         </is>
       </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
-          <t>14h 20m</t>
+          <t>25m</t>
         </is>
       </c>
       <c r="F116" s="0" t="n">
-        <v>860</v>
+        <v>25</v>
       </c>
       <c r="G116" s="0" t="b">
         <v>0</v>
@@ -4181,30 +5438,41 @@
         <f>IF(G116, TEXT(F116/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t>mod_691e93b0ef475f2d</t>
+        </is>
+      </c>
+      <c r="J116" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K116" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified PCM Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
-          <t>What's New in Enterprise Profitability and Cost Management</t>
+          <t>What's New for Common Cloud EPM components</t>
         </is>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
-          <t>47m</t>
+          <t>2h 38m</t>
         </is>
       </c>
       <c r="F117" s="0" t="n">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="G117" s="0" t="b">
         <v>0</v>
@@ -4213,30 +5481,41 @@
         <f>IF(G117, TEXT(F117/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I117" s="0" t="inlineStr">
+        <is>
+          <t>mod_943f75a271ce5e2c</t>
+        </is>
+      </c>
+      <c r="J117" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K117" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified PCM Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
         <is>
-          <t>What's New for Common Cloud EPM components</t>
+          <t>Oracle Financial Consolidation and Close 2025 Implementation Professional (1Z0-1081-25-JPN)</t>
         </is>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>1h 31m</t>
         </is>
       </c>
       <c r="F118" s="0" t="n">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="G118" s="0" t="b">
         <v>0</v>
@@ -4245,21 +5524,32 @@
         <f>IF(G118, TEXT(F118/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
       </c>
+      <c r="I118" s="0" t="inlineStr">
+        <is>
+          <t>mod_3a3a359e1e225aab</t>
+        </is>
+      </c>
+      <c r="J118" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K118" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t>Oracle EPM</t>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
         </is>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>Become a Certified PCM Implementer</t>
+          <t>Become a Certified FCC Implementer</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
         <is>
-          <t>Oracle Profitability and Cost Management 2026 Implementation Professional (1Z0-1082-26)</t>
+          <t>Oracle Financial Consolidation and Close 2026 Implementation Professional (1Z0-1081-26)</t>
         </is>
       </c>
       <c r="E119" s="0" t="inlineStr">
@@ -4276,6 +5566,17 @@
       <c r="H119" s="0">
         <f>IF(G119, TEXT(F119/SUMIF($G$2:$G$119, TRUE, $F$2:$F$119), "0.00%"), "0.00%")</f>
         <v/>
+      </c>
+      <c r="I119" s="0" t="inlineStr">
+        <is>
+          <t>mod_ea2d9b877f0e5a3d</t>
+        </is>
+      </c>
+      <c r="J119" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K119" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4665,7 +5966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4719,6 +6020,36 @@
           <t>Tracking Status</t>
         </is>
       </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>Planned Start Date</t>
+        </is>
+      </c>
+      <c r="L1" s="0" t="inlineStr">
+        <is>
+          <t>Module ID</t>
+        </is>
+      </c>
+      <c r="M1" s="0" t="inlineStr">
+        <is>
+          <t>Enrollment ID</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="O1" s="0" t="inlineStr">
+        <is>
+          <t>Planned Start Offset Minutes</t>
+        </is>
+      </c>
+      <c r="P1" s="0" t="inlineStr">
+        <is>
+          <t>Planned End Offset Minutes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -4743,17 +6074,17 @@
         </is>
       </c>
       <c r="F2" s="0" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>46246</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>Slow</t>
+          <t>On-track</t>
         </is>
       </c>
     </row>
@@ -4790,6 +6121,19 @@
           <t>Slow</t>
         </is>
       </c>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>mod_462dc0b7059255f6</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N3" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -4824,6 +6168,19 @@
           <t>Slow</t>
         </is>
       </c>
+      <c r="L4" s="0" t="inlineStr">
+        <is>
+          <t>mod_d43fe969b8f7585f</t>
+        </is>
+      </c>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N4" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -4858,6 +6215,19 @@
           <t>Slow</t>
         </is>
       </c>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t>mod_de85a4a7c60958b8</t>
+        </is>
+      </c>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N5" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -4892,6 +6262,19 @@
           <t>Slow</t>
         </is>
       </c>
+      <c r="L6" s="0" t="inlineStr">
+        <is>
+          <t>mod_126d66d0c0775a75</t>
+        </is>
+      </c>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N6" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -4919,12 +6302,34 @@
         <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="L7" s="0" t="inlineStr">
+        <is>
+          <t>mod_09ac3ee975bc5f6a</t>
+        </is>
+      </c>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -4953,12 +6358,34 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>46249</v>
+      </c>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t>mod_6dbc960605d1508a</t>
+        </is>
+      </c>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="P8" s="0" t="n">
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -4987,12 +6414,34 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>46252</v>
+      </c>
+      <c r="L9" s="0" t="inlineStr">
+        <is>
+          <t>mod_2607a6c4fd83529d</t>
+        </is>
+      </c>
+      <c r="M9" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" s="0" t="n">
+        <v>392</v>
+      </c>
+      <c r="P9" s="0" t="n">
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -5021,12 +6470,34 @@
         <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>46253</v>
+      </c>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t>mod_b13ff0e384fd58c7</t>
+        </is>
+      </c>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="P10" s="0" t="n">
+        <v>414</v>
       </c>
     </row>
     <row r="11">
@@ -5055,12 +6526,34 @@
         <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>46253</v>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>mod_6ce8d9eef86f5fb4</t>
+        </is>
+      </c>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0" t="n">
+        <v>414</v>
+      </c>
+      <c r="P11" s="0" t="n">
+        <v>329</v>
       </c>
     </row>
     <row r="12">
@@ -5089,12 +6582,34 @@
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="L12" s="0" t="inlineStr">
+        <is>
+          <t>mod_30b53fb973b05c52</t>
+        </is>
+      </c>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="P12" s="0" t="n">
+        <v>420</v>
       </c>
     </row>
     <row r="13">
@@ -5123,12 +6638,34 @@
         <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
+        <is>
+          <t>mod_a296935b855d5b67</t>
+        </is>
+      </c>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" s="0" t="n">
+        <v>420</v>
+      </c>
+      <c r="P13" s="0" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -5164,6 +6701,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t>mod_cca5089845875b1a</t>
+        </is>
+      </c>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N14" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
@@ -5198,6 +6748,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L15" s="0" t="inlineStr">
+        <is>
+          <t>mod_29d398f2f2cf554b</t>
+        </is>
+      </c>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N15" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
@@ -5232,6 +6795,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L16" s="0" t="inlineStr">
+        <is>
+          <t>mod_9f158a8eb28f5300</t>
+        </is>
+      </c>
+      <c r="M16" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N16" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
@@ -5266,6 +6842,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t>mod_3122658003f05166</t>
+        </is>
+      </c>
+      <c r="M17" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N17" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -5300,6 +6889,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L18" s="0" t="inlineStr">
+        <is>
+          <t>mod_691e93b0ef475f2d</t>
+        </is>
+      </c>
+      <c r="M18" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N18" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
@@ -5334,6 +6936,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L19" s="0" t="inlineStr">
+        <is>
+          <t>mod_943f75a271ce5e2c</t>
+        </is>
+      </c>
+      <c r="M19" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N19" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
@@ -5368,6 +6983,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L20" s="0" t="inlineStr">
+        <is>
+          <t>mod_3a3a359e1e225aab</t>
+        </is>
+      </c>
+      <c r="M20" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N20" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
@@ -5402,6 +7030,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L21" s="0" t="inlineStr">
+        <is>
+          <t>mod_ea2d9b877f0e5a3d</t>
+        </is>
+      </c>
+      <c r="M21" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="N21" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
@@ -5436,6 +7077,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L22" s="0" t="inlineStr">
+        <is>
+          <t>mod_227a4ac970765faf</t>
+        </is>
+      </c>
+      <c r="M22" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N22" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
@@ -5470,6 +7124,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L23" s="0" t="inlineStr">
+        <is>
+          <t>mod_462dc0b7059255f6</t>
+        </is>
+      </c>
+      <c r="M23" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N23" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
@@ -5504,6 +7171,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L24" s="0" t="inlineStr">
+        <is>
+          <t>mod_d43fe969b8f7585f</t>
+        </is>
+      </c>
+      <c r="M24" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N24" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
@@ -5538,6 +7218,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L25" s="0" t="inlineStr">
+        <is>
+          <t>mod_de85a4a7c60958b8</t>
+        </is>
+      </c>
+      <c r="M25" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N25" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
@@ -5572,6 +7265,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L26" s="0" t="inlineStr">
+        <is>
+          <t>mod_126d66d0c0775a75</t>
+        </is>
+      </c>
+      <c r="M26" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N26" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
@@ -5599,12 +7305,34 @@
         <v>0</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>46254</v>
+        <v>46249</v>
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="L27" s="0" t="inlineStr">
+        <is>
+          <t>mod_09ac3ee975bc5f6a</t>
+        </is>
+      </c>
+      <c r="M27" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="0" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="28">
@@ -5633,12 +7361,34 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>46256</v>
+        <v>46252</v>
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>46249</v>
+      </c>
+      <c r="L28" s="0" t="inlineStr">
+        <is>
+          <t>mod_6dbc960605d1508a</t>
+        </is>
+      </c>
+      <c r="M28" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="P28" s="0" t="n">
+        <v>392</v>
       </c>
     </row>
     <row r="29">
@@ -5667,12 +7417,34 @@
         <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>46252</v>
+      </c>
+      <c r="L29" s="0" t="inlineStr">
+        <is>
+          <t>mod_2607a6c4fd83529d</t>
+        </is>
+      </c>
+      <c r="M29" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" s="0" t="n">
+        <v>392</v>
+      </c>
+      <c r="P29" s="0" t="n">
+        <v>312</v>
       </c>
     </row>
     <row r="30">
@@ -5701,12 +7473,34 @@
         <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>46253</v>
+      </c>
+      <c r="L30" s="0" t="inlineStr">
+        <is>
+          <t>mod_b13ff0e384fd58c7</t>
+        </is>
+      </c>
+      <c r="M30" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="P30" s="0" t="n">
+        <v>414</v>
       </c>
     </row>
     <row r="31">
@@ -5735,12 +7529,34 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>46253</v>
+      </c>
+      <c r="L31" s="0" t="inlineStr">
+        <is>
+          <t>mod_6ce8d9eef86f5fb4</t>
+        </is>
+      </c>
+      <c r="M31" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" s="0" t="n">
+        <v>414</v>
+      </c>
+      <c r="P31" s="0" t="n">
+        <v>329</v>
       </c>
     </row>
     <row r="32">
@@ -5769,12 +7585,34 @@
         <v>0</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="L32" s="0" t="inlineStr">
+        <is>
+          <t>mod_30b53fb973b05c52</t>
+        </is>
+      </c>
+      <c r="M32" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="P32" s="0" t="n">
+        <v>420</v>
       </c>
     </row>
     <row r="33">
@@ -5803,12 +7641,34 @@
         <v>0</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="L33" s="0" t="inlineStr">
+        <is>
+          <t>mod_a296935b855d5b67</t>
+        </is>
+      </c>
+      <c r="M33" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N33" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" s="0" t="n">
+        <v>420</v>
+      </c>
+      <c r="P33" s="0" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="34">
@@ -5844,6 +7704,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L34" s="0" t="inlineStr">
+        <is>
+          <t>mod_cca5089845875b1a</t>
+        </is>
+      </c>
+      <c r="M34" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N34" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
@@ -5878,6 +7751,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L35" s="0" t="inlineStr">
+        <is>
+          <t>mod_29d398f2f2cf554b</t>
+        </is>
+      </c>
+      <c r="M35" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N35" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
@@ -5912,6 +7798,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L36" s="0" t="inlineStr">
+        <is>
+          <t>mod_9f158a8eb28f5300</t>
+        </is>
+      </c>
+      <c r="M36" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N36" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
@@ -5946,6 +7845,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L37" s="0" t="inlineStr">
+        <is>
+          <t>mod_3122658003f05166</t>
+        </is>
+      </c>
+      <c r="M37" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N37" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
@@ -5980,6 +7892,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L38" s="0" t="inlineStr">
+        <is>
+          <t>mod_691e93b0ef475f2d</t>
+        </is>
+      </c>
+      <c r="M38" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N38" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
@@ -6014,6 +7939,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L39" s="0" t="inlineStr">
+        <is>
+          <t>mod_943f75a271ce5e2c</t>
+        </is>
+      </c>
+      <c r="M39" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N39" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
@@ -6048,6 +7986,19 @@
           <t>On-track</t>
         </is>
       </c>
+      <c r="L40" s="0" t="inlineStr">
+        <is>
+          <t>mod_3a3a359e1e225aab</t>
+        </is>
+      </c>
+      <c r="M40" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N40" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
@@ -6081,6 +8032,19 @@
         <is>
           <t>On-track</t>
         </is>
+      </c>
+      <c r="L41" s="0" t="inlineStr">
+        <is>
+          <t>mod_ea2d9b877f0e5a3d</t>
+        </is>
+      </c>
+      <c r="M41" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="N41" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -6134,7 +8098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6178,6 +8142,21 @@
           <t>Daily Hours</t>
         </is>
       </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Enrollment ID</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Target ID</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>Target Version</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -6196,20 +8175,33 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>46261</v>
+        <v>46255</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>6</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H2" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>enr_e061a7258b5e5c8a</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>plan_d57466e39220532e</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -6231,16 +8223,165 @@
         <v>46246</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>46267</v>
+        <v>46255</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>6</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H3" s="0" t="n">
         <v>8</v>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>enr_5e2fbccfdd915503</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>plan_d57466e39220532e</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Plan ID</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Plan Name</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Plan Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Source Plan ID</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Display Order</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Updated At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>plan_7abc5a79cae55e52</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Pigments Learning</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr"/>
+      <c r="E2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>46247.65279840278</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>plan_f3d5edc7c32f5577</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr"/>
+      <c r="E3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>46247.65279841435</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>plan_d57466e39220532e</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Oracle EPM - Q3 2026 - Fast learning</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>plan_f3d5edc7c32f5577</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>46247.65279841435</v>
       </c>
     </row>
   </sheetData>
